--- a/research/traditional_assets/database/data/luxembourg/luxembourg_auto_parts.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_auto_parts.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09736887025547922</v>
+        <v>0.09715980929306205</v>
       </c>
       <c r="C2">
-        <v>526.4349366210433</v>
+        <v>521.4901995243274</v>
       </c>
       <c r="D2">
-        <v>378.7349366210433</v>
+        <v>379.3451995243274</v>
       </c>
       <c r="E2">
-        <v>-336.8</v>
+        <v>-331.245</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.555</v>
       </c>
       <c r="G2">
         <v>147.7</v>
@@ -1439,28 +1439,28 @@
         <v>63.325</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2794165</v>
       </c>
       <c r="N2">
-        <v>63.325</v>
+        <v>63.04558350000001</v>
       </c>
       <c r="O2">
-        <v>15.793255</v>
+        <v>15.7235685249</v>
       </c>
       <c r="P2">
-        <v>47.531745</v>
+        <v>47.3220149751</v>
       </c>
       <c r="Q2">
-        <v>83.831745</v>
+        <v>83.6220149751</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09736887025547922</v>
+        <v>0.09775985605359802</v>
       </c>
       <c r="T2">
-        <v>1.190966980496056</v>
+        <v>1.199996675602726</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>226.6330012722943</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09715980929306205</v>
+        <v>0.09695074833064488</v>
       </c>
       <c r="C3">
-        <v>521.4901995243274</v>
+        <v>516.5474322583949</v>
       </c>
       <c r="D3">
-        <v>379.3451995243274</v>
+        <v>379.9574322583949</v>
       </c>
       <c r="E3">
-        <v>-331.245</v>
+        <v>-325.69</v>
       </c>
       <c r="F3">
-        <v>5.555</v>
+        <v>11.11</v>
       </c>
       <c r="G3">
         <v>147.7</v>
@@ -1521,28 +1521,28 @@
         <v>63.325</v>
       </c>
       <c r="M3">
-        <v>0.2794165</v>
+        <v>0.5588329999999999</v>
       </c>
       <c r="N3">
-        <v>63.04558350000001</v>
+        <v>62.766167</v>
       </c>
       <c r="O3">
-        <v>15.7235685249</v>
+        <v>15.6538820498</v>
       </c>
       <c r="P3">
-        <v>47.3220149751</v>
+        <v>47.1122849502</v>
       </c>
       <c r="Q3">
-        <v>83.6220149751</v>
+        <v>83.41228495019999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09775985605359802</v>
+        <v>0.09815882115371927</v>
       </c>
       <c r="T3">
-        <v>1.199996675602726</v>
+        <v>1.209210650201369</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>226.6330012722943</v>
+        <v>113.3165006361471</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09695074833064488</v>
+        <v>0.09674168736822771</v>
       </c>
       <c r="C4">
-        <v>516.5474322583949</v>
+        <v>511.6066443761101</v>
       </c>
       <c r="D4">
-        <v>379.9574322583949</v>
+        <v>380.5716443761101</v>
       </c>
       <c r="E4">
-        <v>-325.69</v>
+        <v>-320.135</v>
       </c>
       <c r="F4">
-        <v>11.11</v>
+        <v>16.665</v>
       </c>
       <c r="G4">
         <v>147.7</v>
@@ -1603,28 +1603,28 @@
         <v>63.325</v>
       </c>
       <c r="M4">
-        <v>0.5588329999999999</v>
+        <v>0.8382494999999999</v>
       </c>
       <c r="N4">
-        <v>62.766167</v>
+        <v>62.4867505</v>
       </c>
       <c r="O4">
-        <v>15.6538820498</v>
+        <v>15.5841955747</v>
       </c>
       <c r="P4">
-        <v>47.1122849502</v>
+        <v>46.9025549253</v>
       </c>
       <c r="Q4">
-        <v>83.41228495019999</v>
+        <v>83.20255492529999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09815882115371927</v>
+        <v>0.09856601233837908</v>
       </c>
       <c r="T4">
-        <v>1.209210650201369</v>
+        <v>1.218614603657716</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>113.3165006361471</v>
+        <v>75.54433375743142</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09674168736822771</v>
+        <v>0.09653262640581053</v>
       </c>
       <c r="C5">
-        <v>511.6066443761101</v>
+        <v>506.6678454922073</v>
       </c>
       <c r="D5">
-        <v>380.5716443761101</v>
+        <v>381.1878454922074</v>
       </c>
       <c r="E5">
-        <v>-320.135</v>
+        <v>-314.58</v>
       </c>
       <c r="F5">
-        <v>16.665</v>
+        <v>22.22</v>
       </c>
       <c r="G5">
         <v>147.7</v>
@@ -1685,28 +1685,28 @@
         <v>63.325</v>
       </c>
       <c r="M5">
-        <v>0.8382494999999999</v>
+        <v>1.117666</v>
       </c>
       <c r="N5">
-        <v>62.4867505</v>
+        <v>62.207334</v>
       </c>
       <c r="O5">
-        <v>15.5841955747</v>
+        <v>15.5145090996</v>
       </c>
       <c r="P5">
-        <v>46.9025549253</v>
+        <v>46.6928249004</v>
       </c>
       <c r="Q5">
-        <v>83.20255492529999</v>
+        <v>82.9928249004</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09856601233837908</v>
+        <v>0.09898168667271931</v>
       </c>
       <c r="T5">
-        <v>1.218614603657716</v>
+        <v>1.22821447281107</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>75.54433375743142</v>
+        <v>56.65825031807357</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09653262640581053</v>
+        <v>0.09632356544339338</v>
       </c>
       <c r="C6">
-        <v>506.6678454922073</v>
+        <v>501.7310452837926</v>
       </c>
       <c r="D6">
-        <v>381.1878454922074</v>
+        <v>381.8060452837926</v>
       </c>
       <c r="E6">
-        <v>-314.58</v>
+        <v>-309.025</v>
       </c>
       <c r="F6">
-        <v>22.22</v>
+        <v>27.775</v>
       </c>
       <c r="G6">
         <v>147.7</v>
@@ -1767,28 +1767,28 @@
         <v>63.325</v>
       </c>
       <c r="M6">
-        <v>1.117666</v>
+        <v>1.3970825</v>
       </c>
       <c r="N6">
-        <v>62.207334</v>
+        <v>61.9279175</v>
       </c>
       <c r="O6">
-        <v>15.5145090996</v>
+        <v>15.4448226245</v>
       </c>
       <c r="P6">
-        <v>46.6928249004</v>
+        <v>46.4830948755</v>
       </c>
       <c r="Q6">
-        <v>82.9928249004</v>
+        <v>82.7830948755</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09898168667271931</v>
+        <v>0.09940611204567724</v>
       </c>
       <c r="T6">
-        <v>1.22821447281107</v>
+        <v>1.238016444472916</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>56.65825031807357</v>
+        <v>45.32660025445885</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09632356544339338</v>
+        <v>0.09611450448097621</v>
       </c>
       <c r="C7">
-        <v>501.7310452837926</v>
+        <v>496.7962534908499</v>
       </c>
       <c r="D7">
-        <v>381.8060452837926</v>
+        <v>382.4262534908499</v>
       </c>
       <c r="E7">
-        <v>-309.025</v>
+        <v>-303.47</v>
       </c>
       <c r="F7">
-        <v>27.775</v>
+        <v>33.33000000000001</v>
       </c>
       <c r="G7">
         <v>147.7</v>
@@ -1849,28 +1849,28 @@
         <v>63.325</v>
       </c>
       <c r="M7">
-        <v>1.3970825</v>
+        <v>1.676499</v>
       </c>
       <c r="N7">
-        <v>61.9279175</v>
+        <v>61.648501</v>
       </c>
       <c r="O7">
-        <v>15.4448226245</v>
+        <v>15.3751361494</v>
       </c>
       <c r="P7">
-        <v>46.4830948755</v>
+        <v>46.2733648506</v>
       </c>
       <c r="Q7">
-        <v>82.7830948755</v>
+        <v>82.5733648506</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09940611204567724</v>
+        <v>0.09983956774571937</v>
       </c>
       <c r="T7">
-        <v>1.238016444472916</v>
+        <v>1.248026968723311</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>45.32660025445885</v>
+        <v>37.7721668787157</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09611450448097621</v>
+        <v>0.09590544351855906</v>
       </c>
       <c r="C8">
-        <v>496.7962534908499</v>
+        <v>491.863479916753</v>
       </c>
       <c r="D8">
-        <v>382.4262534908499</v>
+        <v>383.0484799167531</v>
       </c>
       <c r="E8">
-        <v>-303.47</v>
+        <v>-297.915</v>
       </c>
       <c r="F8">
-        <v>33.33</v>
+        <v>38.885</v>
       </c>
       <c r="G8">
         <v>147.7</v>
@@ -1931,28 +1931,28 @@
         <v>63.325</v>
       </c>
       <c r="M8">
-        <v>1.676499</v>
+        <v>1.9559155</v>
       </c>
       <c r="N8">
-        <v>61.648501</v>
+        <v>61.3690845</v>
       </c>
       <c r="O8">
-        <v>15.3751361494</v>
+        <v>15.3054496743</v>
       </c>
       <c r="P8">
-        <v>46.2733648506</v>
+        <v>46.0636348257</v>
       </c>
       <c r="Q8">
-        <v>82.5733648506</v>
+        <v>82.36363482569999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09983956774571937</v>
+        <v>0.1002823450737194</v>
       </c>
       <c r="T8">
-        <v>1.248026968723311</v>
+        <v>1.258252773065114</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>37.77216687871572</v>
+        <v>32.37614303889918</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09590544351855905</v>
+        <v>0.09569638255614189</v>
       </c>
       <c r="C9">
-        <v>491.8634799167531</v>
+        <v>486.9327344287825</v>
       </c>
       <c r="D9">
-        <v>383.0484799167531</v>
+        <v>383.6727344287825</v>
       </c>
       <c r="E9">
-        <v>-297.915</v>
+        <v>-292.36</v>
       </c>
       <c r="F9">
-        <v>38.88500000000001</v>
+        <v>44.44</v>
       </c>
       <c r="G9">
         <v>147.7</v>
@@ -2013,28 +2013,28 @@
         <v>63.325</v>
       </c>
       <c r="M9">
-        <v>1.9559155</v>
+        <v>2.235332</v>
       </c>
       <c r="N9">
-        <v>61.3690845</v>
+        <v>61.089668</v>
       </c>
       <c r="O9">
-        <v>15.3054496743</v>
+        <v>15.2357631992</v>
       </c>
       <c r="P9">
-        <v>46.0636348257</v>
+        <v>45.8539048008</v>
       </c>
       <c r="Q9">
-        <v>82.36363482569999</v>
+        <v>82.15390480080001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1002823450737194</v>
+        <v>0.1007347479958064</v>
       </c>
       <c r="T9">
-        <v>1.258252773065114</v>
+        <v>1.268700877501303</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>32.37614303889917</v>
+        <v>28.32912515903678</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09569638255614189</v>
+        <v>0.09548732159372472</v>
       </c>
       <c r="C10">
-        <v>486.9327344287825</v>
+        <v>482.004026958646</v>
       </c>
       <c r="D10">
-        <v>383.6727344287825</v>
+        <v>384.299026958646</v>
       </c>
       <c r="E10">
-        <v>-292.36</v>
+        <v>-286.805</v>
       </c>
       <c r="F10">
-        <v>44.44</v>
+        <v>49.995</v>
       </c>
       <c r="G10">
         <v>147.7</v>
@@ -2095,28 +2095,28 @@
         <v>63.325</v>
       </c>
       <c r="M10">
-        <v>2.235332</v>
+        <v>2.5147485</v>
       </c>
       <c r="N10">
-        <v>61.089668</v>
+        <v>60.81025150000001</v>
       </c>
       <c r="O10">
-        <v>15.2357631992</v>
+        <v>15.1660767241</v>
       </c>
       <c r="P10">
-        <v>45.8539048008</v>
+        <v>45.64417477590001</v>
       </c>
       <c r="Q10">
-        <v>82.15390480080001</v>
+        <v>81.9441747759</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1007347479958064</v>
+        <v>0.1011970938392579</v>
       </c>
       <c r="T10">
-        <v>1.268700877501303</v>
+        <v>1.279378610606419</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.32912515903678</v>
+        <v>25.18144458581047</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09548732159372472</v>
+        <v>0.09527826063130757</v>
       </c>
       <c r="C11">
-        <v>482.004026958646</v>
+        <v>477.0773675030062</v>
       </c>
       <c r="D11">
-        <v>384.299026958646</v>
+        <v>384.9273675030062</v>
       </c>
       <c r="E11">
-        <v>-286.805</v>
+        <v>-281.25</v>
       </c>
       <c r="F11">
-        <v>49.995</v>
+        <v>55.55</v>
       </c>
       <c r="G11">
         <v>147.7</v>
@@ -2177,28 +2177,28 @@
         <v>63.325</v>
       </c>
       <c r="M11">
-        <v>2.5147485</v>
+        <v>2.794165</v>
       </c>
       <c r="N11">
-        <v>60.81025150000001</v>
+        <v>60.530835</v>
       </c>
       <c r="O11">
-        <v>15.1660767241</v>
+        <v>15.096390249</v>
       </c>
       <c r="P11">
-        <v>45.64417477590001</v>
+        <v>45.434444751</v>
       </c>
       <c r="Q11">
-        <v>81.9441747759</v>
+        <v>81.734444751</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1011970938392579</v>
+        <v>0.1016697140347862</v>
       </c>
       <c r="T11">
-        <v>1.279378610606419</v>
+        <v>1.290293626669427</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.18144458581047</v>
+        <v>22.66330012722943</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09527826063130757</v>
+        <v>0.09506919966889041</v>
       </c>
       <c r="C12">
-        <v>477.0773675030062</v>
+        <v>472.152766124012</v>
       </c>
       <c r="D12">
-        <v>384.9273675030062</v>
+        <v>385.5577661240121</v>
       </c>
       <c r="E12">
-        <v>-281.25</v>
+        <v>-275.695</v>
       </c>
       <c r="F12">
-        <v>55.55</v>
+        <v>61.105</v>
       </c>
       <c r="G12">
         <v>147.7</v>
@@ -2259,28 +2259,28 @@
         <v>63.325</v>
       </c>
       <c r="M12">
-        <v>2.794165</v>
+        <v>3.0735815</v>
       </c>
       <c r="N12">
-        <v>60.530835</v>
+        <v>60.2514185</v>
       </c>
       <c r="O12">
-        <v>15.096390249</v>
+        <v>15.0267037739</v>
       </c>
       <c r="P12">
-        <v>45.434444751</v>
+        <v>45.2247147261</v>
       </c>
       <c r="Q12">
-        <v>81.734444751</v>
+        <v>81.5247147261</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1016697140347862</v>
+        <v>0.1021529549088656</v>
       </c>
       <c r="T12">
-        <v>1.290293626669427</v>
+        <v>1.301453923992278</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.66330012722942</v>
+        <v>20.60300011566311</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09506919966889041</v>
+        <v>0.09486013870647321</v>
       </c>
       <c r="C13">
-        <v>472.152766124012</v>
+        <v>467.2302329498367</v>
       </c>
       <c r="D13">
-        <v>385.5577661240121</v>
+        <v>386.1902329498366</v>
       </c>
       <c r="E13">
-        <v>-275.695</v>
+        <v>-270.14</v>
       </c>
       <c r="F13">
-        <v>61.105</v>
+        <v>66.66</v>
       </c>
       <c r="G13">
         <v>147.7</v>
@@ -2341,28 +2341,28 @@
         <v>63.325</v>
       </c>
       <c r="M13">
-        <v>3.0735815</v>
+        <v>3.352997999999999</v>
       </c>
       <c r="N13">
-        <v>60.2514185</v>
+        <v>59.972002</v>
       </c>
       <c r="O13">
-        <v>15.0267037739</v>
+        <v>14.9570172988</v>
       </c>
       <c r="P13">
-        <v>45.2247147261</v>
+        <v>45.0149847012</v>
       </c>
       <c r="Q13">
-        <v>81.5247147261</v>
+        <v>81.31498470119999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1021529549088656</v>
+        <v>0.1026471785300832</v>
       </c>
       <c r="T13">
-        <v>1.301453923992278</v>
+        <v>1.312867864436102</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.60300011566311</v>
+        <v>18.88608343935786</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09486013870647321</v>
+        <v>0.09465107774405607</v>
       </c>
       <c r="C14">
-        <v>467.2302329498367</v>
+        <v>462.309778175218</v>
       </c>
       <c r="D14">
-        <v>386.1902329498366</v>
+        <v>386.8247781752179</v>
       </c>
       <c r="E14">
-        <v>-270.14</v>
+        <v>-264.585</v>
       </c>
       <c r="F14">
-        <v>66.66</v>
+        <v>72.215</v>
       </c>
       <c r="G14">
         <v>147.7</v>
@@ -2423,28 +2423,28 @@
         <v>63.325</v>
       </c>
       <c r="M14">
-        <v>3.352997999999999</v>
+        <v>3.6324145</v>
       </c>
       <c r="N14">
-        <v>59.972002</v>
+        <v>59.6925855</v>
       </c>
       <c r="O14">
-        <v>14.9570172988</v>
+        <v>14.8873308237</v>
       </c>
       <c r="P14">
-        <v>45.0149847012</v>
+        <v>44.8052546763</v>
       </c>
       <c r="Q14">
-        <v>81.31498470119999</v>
+        <v>81.10525467629999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1026471785300832</v>
+        <v>0.1031527636138576</v>
       </c>
       <c r="T14">
-        <v>1.312867864436102</v>
+        <v>1.324544194315417</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.88608343935786</v>
+        <v>17.43330779017648</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09465107774405607</v>
+        <v>0.0944420167816389</v>
       </c>
       <c r="C15">
-        <v>462.309778175218</v>
+        <v>457.3914120620086</v>
       </c>
       <c r="D15">
-        <v>386.8247781752179</v>
+        <v>387.4614120620087</v>
       </c>
       <c r="E15">
-        <v>-264.585</v>
+        <v>-259.03</v>
       </c>
       <c r="F15">
-        <v>72.215</v>
+        <v>77.77000000000001</v>
       </c>
       <c r="G15">
         <v>147.7</v>
@@ -2505,28 +2505,28 @@
         <v>63.325</v>
       </c>
       <c r="M15">
-        <v>3.6324145</v>
+        <v>3.911831</v>
       </c>
       <c r="N15">
-        <v>59.6925855</v>
+        <v>59.413169</v>
       </c>
       <c r="O15">
-        <v>14.8873308237</v>
+        <v>14.8176443486</v>
       </c>
       <c r="P15">
-        <v>44.8052546763</v>
+        <v>44.5955246514</v>
       </c>
       <c r="Q15">
-        <v>81.10525467629999</v>
+        <v>80.8955246514</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1031527636138576</v>
+        <v>0.1036701064902778</v>
       </c>
       <c r="T15">
-        <v>1.324544194315417</v>
+        <v>1.336492066750065</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.43330779017648</v>
+        <v>16.18807151944959</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0944420167816389</v>
+        <v>0.09423295581922173</v>
       </c>
       <c r="C16">
-        <v>457.3914120620086</v>
+        <v>452.475144939728</v>
       </c>
       <c r="D16">
-        <v>387.4614120620087</v>
+        <v>388.1001449397281</v>
       </c>
       <c r="E16">
-        <v>-259.03</v>
+        <v>-253.475</v>
       </c>
       <c r="F16">
-        <v>77.77000000000001</v>
+        <v>83.32500000000002</v>
       </c>
       <c r="G16">
         <v>147.7</v>
@@ -2587,28 +2587,28 @@
         <v>63.325</v>
       </c>
       <c r="M16">
-        <v>3.911831</v>
+        <v>4.1912475</v>
       </c>
       <c r="N16">
-        <v>59.413169</v>
+        <v>59.1337525</v>
       </c>
       <c r="O16">
-        <v>14.8176443486</v>
+        <v>14.7479578735</v>
       </c>
       <c r="P16">
-        <v>44.5955246514</v>
+        <v>44.3857946265</v>
       </c>
       <c r="Q16">
-        <v>80.8955246514</v>
+        <v>80.6857946265</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1036701064902778</v>
+        <v>0.1041996221402609</v>
       </c>
       <c r="T16">
-        <v>1.336492066750065</v>
+        <v>1.348721065594939</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.18807151944959</v>
+        <v>15.10886675148628</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09423295581922173</v>
+        <v>0.09402389485680455</v>
       </c>
       <c r="C17">
-        <v>452.4751449397281</v>
+        <v>447.560987206121</v>
       </c>
       <c r="D17">
-        <v>388.1001449397281</v>
+        <v>388.7409872061211</v>
       </c>
       <c r="E17">
-        <v>-253.475</v>
+        <v>-247.92</v>
       </c>
       <c r="F17">
-        <v>83.325</v>
+        <v>88.88</v>
       </c>
       <c r="G17">
         <v>147.7</v>
@@ -2669,28 +2669,28 @@
         <v>63.325</v>
       </c>
       <c r="M17">
-        <v>4.1912475</v>
+        <v>4.470663999999999</v>
       </c>
       <c r="N17">
-        <v>59.1337525</v>
+        <v>58.854336</v>
       </c>
       <c r="O17">
-        <v>14.7479578735</v>
+        <v>14.6782713984</v>
       </c>
       <c r="P17">
-        <v>44.3857946265</v>
+        <v>44.1760646016</v>
       </c>
       <c r="Q17">
-        <v>80.6857946265</v>
+        <v>80.4760646016</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1041996221402609</v>
+        <v>0.1047417453057197</v>
       </c>
       <c r="T17">
-        <v>1.348721065594939</v>
+        <v>1.361241231078978</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.10886675148628</v>
+        <v>14.16456257951839</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09402389485680455</v>
+        <v>0.0938148338943874</v>
       </c>
       <c r="C18">
-        <v>447.560987206121</v>
+        <v>442.6489493277224</v>
       </c>
       <c r="D18">
-        <v>388.7409872061211</v>
+        <v>389.3839493277223</v>
       </c>
       <c r="E18">
-        <v>-247.92</v>
+        <v>-242.365</v>
       </c>
       <c r="F18">
-        <v>88.88</v>
+        <v>94.435</v>
       </c>
       <c r="G18">
         <v>147.7</v>
@@ -2751,28 +2751,28 @@
         <v>63.325</v>
       </c>
       <c r="M18">
-        <v>4.470663999999999</v>
+        <v>4.7500805</v>
       </c>
       <c r="N18">
-        <v>58.854336</v>
+        <v>58.5749195</v>
       </c>
       <c r="O18">
-        <v>14.6782713984</v>
+        <v>14.6085849233</v>
       </c>
       <c r="P18">
-        <v>44.1760646016</v>
+        <v>43.9663345767</v>
       </c>
       <c r="Q18">
-        <v>80.4760646016</v>
+        <v>80.26633457669999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1047417453057197</v>
+        <v>0.1052969316799848</v>
       </c>
       <c r="T18">
-        <v>1.361241231078978</v>
+        <v>1.374063087297571</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.16456257951839</v>
+        <v>13.33135301601731</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0938148338943874</v>
+        <v>0.09380843493197023</v>
       </c>
       <c r="C19">
-        <v>442.6489493277224</v>
+        <v>437.1136627353151</v>
       </c>
       <c r="D19">
-        <v>389.3839493277223</v>
+        <v>389.403662735315</v>
       </c>
       <c r="E19">
-        <v>-242.365</v>
+        <v>-236.81</v>
       </c>
       <c r="F19">
-        <v>94.435</v>
+        <v>99.99000000000001</v>
       </c>
       <c r="G19">
         <v>147.7</v>
@@ -2833,45 +2833,45 @@
         <v>63.325</v>
       </c>
       <c r="M19">
-        <v>4.7500805</v>
+        <v>5.179482</v>
       </c>
       <c r="N19">
-        <v>58.5749195</v>
+        <v>58.145518</v>
       </c>
       <c r="O19">
-        <v>14.6085849233</v>
+        <v>14.5014921892</v>
       </c>
       <c r="P19">
-        <v>43.9663345767</v>
+        <v>43.6440258108</v>
       </c>
       <c r="Q19">
-        <v>80.26633457669999</v>
+        <v>79.9440258108</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1052969316799848</v>
+        <v>0.1058656591853296</v>
       </c>
       <c r="T19">
-        <v>1.374063087297571</v>
+        <v>1.387197671716618</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.2494</v>
       </c>
       <c r="W19">
-        <v>0.03775517999999999</v>
+        <v>0.03888108</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>13.33135301601731</v>
+        <v>12.22612608751223</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09380843493197025</v>
+        <v>0.09361063296955308</v>
       </c>
       <c r="C20">
-        <v>437.113662735315</v>
+        <v>432.1690211167001</v>
       </c>
       <c r="D20">
-        <v>389.403662735315</v>
+        <v>390.0140211167001</v>
       </c>
       <c r="E20">
-        <v>-236.81</v>
+        <v>-231.255</v>
       </c>
       <c r="F20">
-        <v>99.98999999999999</v>
+        <v>105.545</v>
       </c>
       <c r="G20">
         <v>147.7</v>
@@ -2915,28 +2915,28 @@
         <v>63.325</v>
       </c>
       <c r="M20">
-        <v>5.179481999999999</v>
+        <v>5.467231</v>
       </c>
       <c r="N20">
-        <v>58.145518</v>
+        <v>57.857769</v>
       </c>
       <c r="O20">
-        <v>14.5014921892</v>
+        <v>14.4297275886</v>
       </c>
       <c r="P20">
-        <v>43.6440258108</v>
+        <v>43.4280414114</v>
       </c>
       <c r="Q20">
-        <v>79.9440258108</v>
+        <v>79.7280414114</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1058656591853296</v>
+        <v>0.1064484293451272</v>
       </c>
       <c r="T20">
-        <v>1.387197671716618</v>
+        <v>1.400656566862061</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.22612608751223</v>
+        <v>11.58264576711685</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09361063296955308</v>
+        <v>0.09341283100713592</v>
       </c>
       <c r="C21">
-        <v>432.1690211167001</v>
+        <v>427.2262958754999</v>
       </c>
       <c r="D21">
-        <v>390.0140211167001</v>
+        <v>390.6262958754999</v>
       </c>
       <c r="E21">
-        <v>-231.255</v>
+        <v>-225.7</v>
       </c>
       <c r="F21">
-        <v>105.545</v>
+        <v>111.1</v>
       </c>
       <c r="G21">
         <v>147.7</v>
@@ -2997,28 +2997,28 @@
         <v>63.325</v>
       </c>
       <c r="M21">
-        <v>5.467231</v>
+        <v>5.754980000000001</v>
       </c>
       <c r="N21">
-        <v>57.857769</v>
+        <v>57.57002</v>
       </c>
       <c r="O21">
-        <v>14.4297275886</v>
+        <v>14.357962988</v>
       </c>
       <c r="P21">
-        <v>43.4280414114</v>
+        <v>43.212057012</v>
       </c>
       <c r="Q21">
-        <v>79.7280414114</v>
+        <v>79.512057012</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1064484293451272</v>
+        <v>0.1070457687589199</v>
       </c>
       <c r="T21">
-        <v>1.400656566862061</v>
+        <v>1.414451934386141</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.58264576711685</v>
+        <v>11.003513478761</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09341283100713592</v>
+        <v>0.09321502904471875</v>
       </c>
       <c r="C22">
-        <v>427.2262958754999</v>
+        <v>422.2854960513465</v>
       </c>
       <c r="D22">
-        <v>390.6262958754999</v>
+        <v>391.2404960513465</v>
       </c>
       <c r="E22">
-        <v>-225.7</v>
+        <v>-220.145</v>
       </c>
       <c r="F22">
-        <v>111.1</v>
+        <v>116.655</v>
       </c>
       <c r="G22">
         <v>147.7</v>
@@ -3079,28 +3079,28 @@
         <v>63.325</v>
       </c>
       <c r="M22">
-        <v>5.754980000000001</v>
+        <v>6.042729</v>
       </c>
       <c r="N22">
-        <v>57.57002</v>
+        <v>57.282271</v>
       </c>
       <c r="O22">
-        <v>14.357962988</v>
+        <v>14.2861983874</v>
       </c>
       <c r="P22">
-        <v>43.212057012</v>
+        <v>42.9960726126</v>
       </c>
       <c r="Q22">
-        <v>79.512057012</v>
+        <v>79.2960726126</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1070457687589199</v>
+        <v>0.1076582306895174</v>
       </c>
       <c r="T22">
-        <v>1.414451934386141</v>
+        <v>1.428596551720956</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.003513478761</v>
+        <v>10.47953664643905</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09321502904471875</v>
+        <v>0.09301722708230159</v>
       </c>
       <c r="C23">
-        <v>422.2854960513465</v>
+        <v>417.3466307408156</v>
       </c>
       <c r="D23">
-        <v>391.2404960513465</v>
+        <v>391.8566307408155</v>
       </c>
       <c r="E23">
-        <v>-220.145</v>
+        <v>-214.59</v>
       </c>
       <c r="F23">
-        <v>116.655</v>
+        <v>122.21</v>
       </c>
       <c r="G23">
         <v>147.7</v>
@@ -3161,28 +3161,28 @@
         <v>63.325</v>
       </c>
       <c r="M23">
-        <v>6.042729</v>
+        <v>6.330477999999999</v>
       </c>
       <c r="N23">
-        <v>57.282271</v>
+        <v>56.994522</v>
       </c>
       <c r="O23">
-        <v>14.2861983874</v>
+        <v>14.2144337868</v>
       </c>
       <c r="P23">
-        <v>42.9960726126</v>
+        <v>42.7800882132</v>
       </c>
       <c r="Q23">
-        <v>79.2960726126</v>
+        <v>79.0800882132</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1076582306895174</v>
+        <v>0.1082863967721815</v>
       </c>
       <c r="T23">
-        <v>1.428596551720956</v>
+        <v>1.443103851551536</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.47953664643905</v>
+        <v>10.00319407160091</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09301722708230159</v>
+        <v>0.0931129097198844</v>
       </c>
       <c r="C24">
-        <v>417.3466307408156</v>
+        <v>411.4933461022075</v>
       </c>
       <c r="D24">
-        <v>391.8566307408155</v>
+        <v>391.5583461022076</v>
       </c>
       <c r="E24">
-        <v>-214.59</v>
+        <v>-209.035</v>
       </c>
       <c r="F24">
-        <v>122.21</v>
+        <v>127.765</v>
       </c>
       <c r="G24">
         <v>147.7</v>
@@ -3243,45 +3243,45 @@
         <v>63.325</v>
       </c>
       <c r="M24">
-        <v>6.330477999999999</v>
+        <v>6.8354275</v>
       </c>
       <c r="N24">
-        <v>56.994522</v>
+        <v>56.4895725</v>
       </c>
       <c r="O24">
-        <v>14.2144337868</v>
+        <v>14.0884993815</v>
       </c>
       <c r="P24">
-        <v>42.7800882132</v>
+        <v>42.4010731185</v>
       </c>
       <c r="Q24">
-        <v>79.0800882132</v>
+        <v>78.70107311850001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1082863967721815</v>
+        <v>0.1089308788569927</v>
       </c>
       <c r="T24">
-        <v>1.443103851551536</v>
+        <v>1.457987964364729</v>
       </c>
       <c r="U24">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.2494</v>
       </c>
       <c r="W24">
-        <v>0.03888108</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>10.00319407160091</v>
+        <v>9.264234021939375</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0931129097198844</v>
+        <v>0.09292786795746726</v>
       </c>
       <c r="C25">
-        <v>411.4933461022075</v>
+        <v>406.5156129163978</v>
       </c>
       <c r="D25">
-        <v>391.5583461022076</v>
+        <v>392.1356129163979</v>
       </c>
       <c r="E25">
-        <v>-209.035</v>
+        <v>-203.48</v>
       </c>
       <c r="F25">
-        <v>127.765</v>
+        <v>133.32</v>
       </c>
       <c r="G25">
         <v>147.7</v>
@@ -3325,28 +3325,28 @@
         <v>63.325</v>
       </c>
       <c r="M25">
-        <v>6.8354275</v>
+        <v>7.132620000000001</v>
       </c>
       <c r="N25">
-        <v>56.4895725</v>
+        <v>56.19238</v>
       </c>
       <c r="O25">
-        <v>14.0884993815</v>
+        <v>14.014379572</v>
       </c>
       <c r="P25">
-        <v>42.4010731185</v>
+        <v>42.178000428</v>
       </c>
       <c r="Q25">
-        <v>78.70107311850001</v>
+        <v>78.478000428</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1089308788569927</v>
+        <v>0.1095923209966674</v>
       </c>
       <c r="T25">
-        <v>1.457987964364729</v>
+        <v>1.473263764357216</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.264234021939375</v>
+        <v>8.878224271025232</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09292786795746726</v>
+        <v>0.09274282619505007</v>
       </c>
       <c r="C26">
-        <v>406.5156129163979</v>
+        <v>401.5395843500312</v>
       </c>
       <c r="D26">
-        <v>392.1356129163979</v>
+        <v>392.7145843500312</v>
       </c>
       <c r="E26">
-        <v>-203.48</v>
+        <v>-197.925</v>
       </c>
       <c r="F26">
-        <v>133.32</v>
+        <v>138.875</v>
       </c>
       <c r="G26">
         <v>147.7</v>
@@ -3407,28 +3407,28 @@
         <v>63.325</v>
       </c>
       <c r="M26">
-        <v>7.132619999999999</v>
+        <v>7.4298125</v>
       </c>
       <c r="N26">
-        <v>56.19238</v>
+        <v>55.89518750000001</v>
       </c>
       <c r="O26">
-        <v>14.014379572</v>
+        <v>13.9402597625</v>
       </c>
       <c r="P26">
-        <v>42.178000428</v>
+        <v>41.9549277375</v>
       </c>
       <c r="Q26">
-        <v>78.478000428</v>
+        <v>78.2549277375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1095923209966674</v>
+        <v>0.1102714015934001</v>
       </c>
       <c r="T26">
-        <v>1.473263764357216</v>
+        <v>1.488946919016169</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.878224271025234</v>
+        <v>8.523095300184224</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09274282619505007</v>
+        <v>0.09255778443263291</v>
       </c>
       <c r="C27">
-        <v>401.5395843500312</v>
+        <v>396.5652679646643</v>
       </c>
       <c r="D27">
-        <v>392.7145843500312</v>
+        <v>393.2952679646643</v>
       </c>
       <c r="E27">
-        <v>-197.925</v>
+        <v>-192.37</v>
       </c>
       <c r="F27">
-        <v>138.875</v>
+        <v>144.43</v>
       </c>
       <c r="G27">
         <v>147.7</v>
@@ -3489,28 +3489,28 @@
         <v>63.325</v>
       </c>
       <c r="M27">
-        <v>7.4298125</v>
+        <v>7.727005</v>
       </c>
       <c r="N27">
-        <v>55.89518750000001</v>
+        <v>55.597995</v>
       </c>
       <c r="O27">
-        <v>13.9402597625</v>
+        <v>13.866139953</v>
       </c>
       <c r="P27">
-        <v>41.9549277375</v>
+        <v>41.731855047</v>
       </c>
       <c r="Q27">
-        <v>78.2549277375</v>
+        <v>78.03185504699999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1102714015934001</v>
+        <v>0.1109688357197742</v>
       </c>
       <c r="T27">
-        <v>1.488946919016169</v>
+        <v>1.505053942719959</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.523095300184224</v>
+        <v>8.195283942484831</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09255778443263291</v>
+        <v>0.09237274267021575</v>
       </c>
       <c r="C28">
-        <v>396.5652679646643</v>
+        <v>391.5926713666439</v>
       </c>
       <c r="D28">
-        <v>393.2952679646643</v>
+        <v>393.8776713666439</v>
       </c>
       <c r="E28">
-        <v>-192.37</v>
+        <v>-186.815</v>
       </c>
       <c r="F28">
-        <v>144.43</v>
+        <v>149.985</v>
       </c>
       <c r="G28">
         <v>147.7</v>
@@ -3571,28 +3571,28 @@
         <v>63.325</v>
       </c>
       <c r="M28">
-        <v>7.727005</v>
+        <v>8.024197500000001</v>
       </c>
       <c r="N28">
-        <v>55.597995</v>
+        <v>55.3008025</v>
       </c>
       <c r="O28">
-        <v>13.866139953</v>
+        <v>13.7920201435</v>
       </c>
       <c r="P28">
-        <v>41.731855047</v>
+        <v>41.5087823565</v>
       </c>
       <c r="Q28">
-        <v>78.03185504699999</v>
+        <v>77.80878235649999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1109688357197742</v>
+        <v>0.1116853776304325</v>
       </c>
       <c r="T28">
-        <v>1.505053942719959</v>
+        <v>1.521602254744401</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.195283942484831</v>
+        <v>7.891754907577984</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09237274267021575</v>
+        <v>0.09235583530779859</v>
       </c>
       <c r="C29">
-        <v>391.5926713666439</v>
+        <v>386.0909718828884</v>
       </c>
       <c r="D29">
-        <v>393.8776713666439</v>
+        <v>393.9309718828883</v>
       </c>
       <c r="E29">
-        <v>-186.815</v>
+        <v>-181.26</v>
       </c>
       <c r="F29">
-        <v>149.985</v>
+        <v>155.54</v>
       </c>
       <c r="G29">
         <v>147.7</v>
@@ -3653,45 +3653,45 @@
         <v>63.325</v>
       </c>
       <c r="M29">
-        <v>8.024197500000001</v>
+        <v>8.445822000000001</v>
       </c>
       <c r="N29">
-        <v>55.3008025</v>
+        <v>54.879178</v>
       </c>
       <c r="O29">
-        <v>13.7920201435</v>
+        <v>13.6868669932</v>
       </c>
       <c r="P29">
-        <v>41.5087823565</v>
+        <v>41.1923110068</v>
       </c>
       <c r="Q29">
-        <v>77.80878235649999</v>
+        <v>77.49231100680001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1116853776304325</v>
+        <v>0.1124218234830536</v>
       </c>
       <c r="T29">
-        <v>1.521602254744401</v>
+        <v>1.538610242102855</v>
       </c>
       <c r="U29">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.2494</v>
       </c>
       <c r="W29">
-        <v>0.04015709999999999</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>7.891754907577984</v>
+        <v>7.497790031568271</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09235583530779859</v>
+        <v>0.09217679834538142</v>
       </c>
       <c r="C30">
-        <v>386.0909718828884</v>
+        <v>381.1012729393603</v>
       </c>
       <c r="D30">
-        <v>393.9309718828883</v>
+        <v>394.4962729393604</v>
       </c>
       <c r="E30">
-        <v>-181.26</v>
+        <v>-175.705</v>
       </c>
       <c r="F30">
-        <v>155.54</v>
+        <v>161.095</v>
       </c>
       <c r="G30">
         <v>147.7</v>
@@ -3735,28 +3735,28 @@
         <v>63.325</v>
       </c>
       <c r="M30">
-        <v>8.445822000000001</v>
+        <v>8.747458500000002</v>
       </c>
       <c r="N30">
-        <v>54.879178</v>
+        <v>54.5775415</v>
       </c>
       <c r="O30">
-        <v>13.6868669932</v>
+        <v>13.6116388501</v>
       </c>
       <c r="P30">
-        <v>41.1923110068</v>
+        <v>40.9659026499</v>
       </c>
       <c r="Q30">
-        <v>77.49231100680001</v>
+        <v>77.2659026499</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1124218234830536</v>
+        <v>0.1131790142892696</v>
       </c>
       <c r="T30">
-        <v>1.538610242102855</v>
+        <v>1.556097327696758</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.497790031568271</v>
+        <v>7.239245547721088</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09217679834538141</v>
+        <v>0.09199776138296424</v>
       </c>
       <c r="C31">
-        <v>381.1012729393603</v>
+        <v>376.1131987704794</v>
       </c>
       <c r="D31">
-        <v>394.4962729393604</v>
+        <v>395.0631987704793</v>
       </c>
       <c r="E31">
-        <v>-175.705</v>
+        <v>-170.15</v>
       </c>
       <c r="F31">
-        <v>161.095</v>
+        <v>166.65</v>
       </c>
       <c r="G31">
         <v>147.7</v>
@@ -3817,28 +3817,28 @@
         <v>63.325</v>
       </c>
       <c r="M31">
-        <v>8.7474585</v>
+        <v>9.049095000000001</v>
       </c>
       <c r="N31">
-        <v>54.5775415</v>
+        <v>54.275905</v>
       </c>
       <c r="O31">
-        <v>13.6116388501</v>
+        <v>13.536410707</v>
       </c>
       <c r="P31">
-        <v>40.9659026499</v>
+        <v>40.739494293</v>
       </c>
       <c r="Q31">
-        <v>77.2659026499</v>
+        <v>77.03949429299999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1131790142892696</v>
+        <v>0.1139578391185204</v>
       </c>
       <c r="T31">
-        <v>1.556097327696758</v>
+        <v>1.57408404430763</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.239245547721089</v>
+        <v>6.997937362797052</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09199776138296424</v>
+        <v>0.09181872442054707</v>
       </c>
       <c r="C32">
-        <v>376.1131987704794</v>
+        <v>371.1267563911582</v>
       </c>
       <c r="D32">
-        <v>395.0631987704793</v>
+        <v>395.6317563911583</v>
       </c>
       <c r="E32">
-        <v>-170.15</v>
+        <v>-164.595</v>
       </c>
       <c r="F32">
-        <v>166.65</v>
+        <v>172.205</v>
       </c>
       <c r="G32">
         <v>147.7</v>
@@ -3899,28 +3899,28 @@
         <v>63.325</v>
       </c>
       <c r="M32">
-        <v>9.049095000000001</v>
+        <v>9.3507315</v>
       </c>
       <c r="N32">
-        <v>54.275905</v>
+        <v>53.9742685</v>
       </c>
       <c r="O32">
-        <v>13.536410707</v>
+        <v>13.4611825639</v>
       </c>
       <c r="P32">
-        <v>40.739494293</v>
+        <v>40.5130859361</v>
       </c>
       <c r="Q32">
-        <v>77.03949429299999</v>
+        <v>76.81308593609999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1139578391185204</v>
+        <v>0.114759238580503</v>
       </c>
       <c r="T32">
-        <v>1.57408404430763</v>
+        <v>1.592592115023165</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.997937362797052</v>
+        <v>6.772197447868116</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09181872442054707</v>
+        <v>0.09163968745812993</v>
       </c>
       <c r="C33">
-        <v>371.1267563911582</v>
+        <v>366.1419528567505</v>
       </c>
       <c r="D33">
-        <v>395.6317563911583</v>
+        <v>396.2019528567506</v>
       </c>
       <c r="E33">
-        <v>-164.595</v>
+        <v>-159.04</v>
       </c>
       <c r="F33">
-        <v>172.205</v>
+        <v>177.76</v>
       </c>
       <c r="G33">
         <v>147.7</v>
@@ -3981,28 +3981,28 @@
         <v>63.325</v>
       </c>
       <c r="M33">
-        <v>9.3507315</v>
+        <v>9.652367999999999</v>
       </c>
       <c r="N33">
-        <v>53.9742685</v>
+        <v>53.67263200000001</v>
       </c>
       <c r="O33">
-        <v>13.4611825639</v>
+        <v>13.3859544208</v>
       </c>
       <c r="P33">
-        <v>40.5130859361</v>
+        <v>40.2866775792</v>
       </c>
       <c r="Q33">
-        <v>76.81308593609999</v>
+        <v>76.5866775792</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.114759238580503</v>
+        <v>0.115584208614897</v>
       </c>
       <c r="T33">
-        <v>1.592592115023165</v>
+        <v>1.611644540759745</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.772197447868116</v>
+        <v>6.560566277622239</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09163968745812993</v>
+        <v>0.09146065049571274</v>
       </c>
       <c r="C34">
-        <v>366.1419528567505</v>
+        <v>361.1587952633424</v>
       </c>
       <c r="D34">
-        <v>396.2019528567506</v>
+        <v>396.7737952633424</v>
       </c>
       <c r="E34">
-        <v>-159.04</v>
+        <v>-153.485</v>
       </c>
       <c r="F34">
-        <v>177.76</v>
+        <v>183.315</v>
       </c>
       <c r="G34">
         <v>147.7</v>
@@ -4063,28 +4063,28 @@
         <v>63.325</v>
       </c>
       <c r="M34">
-        <v>9.652367999999999</v>
+        <v>9.9540045</v>
       </c>
       <c r="N34">
-        <v>53.67263200000001</v>
+        <v>53.37099550000001</v>
       </c>
       <c r="O34">
-        <v>13.3859544208</v>
+        <v>13.3107262777</v>
       </c>
       <c r="P34">
-        <v>40.2866775792</v>
+        <v>40.06026922230001</v>
       </c>
       <c r="Q34">
-        <v>76.5866775792</v>
+        <v>76.3602692223</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.115584208614897</v>
+        <v>0.1164338046204668</v>
       </c>
       <c r="T34">
-        <v>1.611644540759745</v>
+        <v>1.63126569562279</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.560566277622239</v>
+        <v>6.361761238906412</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09146065049571274</v>
+        <v>0.09128161353329559</v>
       </c>
       <c r="C35">
-        <v>361.1587952633424</v>
+        <v>356.1772907480459</v>
       </c>
       <c r="D35">
-        <v>396.7737952633424</v>
+        <v>397.3472907480459</v>
       </c>
       <c r="E35">
-        <v>-153.485</v>
+        <v>-147.93</v>
       </c>
       <c r="F35">
-        <v>183.315</v>
+        <v>188.87</v>
       </c>
       <c r="G35">
         <v>147.7</v>
@@ -4145,28 +4145,28 @@
         <v>63.325</v>
       </c>
       <c r="M35">
-        <v>9.9540045</v>
+        <v>10.255641</v>
       </c>
       <c r="N35">
-        <v>53.37099550000001</v>
+        <v>53.06935900000001</v>
       </c>
       <c r="O35">
-        <v>13.3107262777</v>
+        <v>13.2354981346</v>
       </c>
       <c r="P35">
-        <v>40.06026922230001</v>
+        <v>39.83386086540001</v>
       </c>
       <c r="Q35">
-        <v>76.3602692223</v>
+        <v>76.13386086540001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1164338046204668</v>
+        <v>0.1173091459595388</v>
       </c>
       <c r="T35">
-        <v>1.63126569562279</v>
+        <v>1.651481430936231</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.361761238906412</v>
+        <v>6.174650614232694</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09128161353329559</v>
+        <v>0.09136528657087842</v>
       </c>
       <c r="C36">
-        <v>356.1772907480459</v>
+        <v>350.3540610614893</v>
       </c>
       <c r="D36">
-        <v>397.3472907480459</v>
+        <v>397.0790610614893</v>
       </c>
       <c r="E36">
-        <v>-147.93</v>
+        <v>-142.375</v>
       </c>
       <c r="F36">
-        <v>188.87</v>
+        <v>194.425</v>
       </c>
       <c r="G36">
         <v>147.7</v>
@@ -4227,45 +4227,45 @@
         <v>63.325</v>
       </c>
       <c r="M36">
-        <v>10.255641</v>
+        <v>10.7517025</v>
       </c>
       <c r="N36">
-        <v>53.06935900000001</v>
+        <v>52.5732975</v>
       </c>
       <c r="O36">
-        <v>13.2354981346</v>
+        <v>13.1117803965</v>
       </c>
       <c r="P36">
-        <v>39.83386086540001</v>
+        <v>39.4615171035</v>
       </c>
       <c r="Q36">
-        <v>76.13386086540001</v>
+        <v>75.7615171035</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1173091459595388</v>
+        <v>0.1182114208782745</v>
       </c>
       <c r="T36">
-        <v>1.651481430936231</v>
+        <v>1.6723191888747</v>
       </c>
       <c r="U36">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V36">
         <v>0.2494</v>
       </c>
       <c r="W36">
-        <v>0.04075757999999999</v>
+        <v>0.04150818</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>6.174650614232694</v>
+        <v>5.889764900023973</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09136528657087842</v>
+        <v>0.09119375560846124</v>
       </c>
       <c r="C37">
-        <v>350.3540610614893</v>
+        <v>345.3493261779739</v>
       </c>
       <c r="D37">
-        <v>397.0790610614893</v>
+        <v>397.629326177974</v>
       </c>
       <c r="E37">
-        <v>-142.375</v>
+        <v>-136.82</v>
       </c>
       <c r="F37">
-        <v>194.425</v>
+        <v>199.98</v>
       </c>
       <c r="G37">
         <v>147.7</v>
@@ -4309,28 +4309,28 @@
         <v>63.325</v>
       </c>
       <c r="M37">
-        <v>10.7517025</v>
+        <v>11.058894</v>
       </c>
       <c r="N37">
-        <v>52.5732975</v>
+        <v>52.266106</v>
       </c>
       <c r="O37">
-        <v>13.1117803965</v>
+        <v>13.0351668364</v>
       </c>
       <c r="P37">
-        <v>39.4615171035</v>
+        <v>39.2309391636</v>
       </c>
       <c r="Q37">
-        <v>75.7615171035</v>
+        <v>75.5309391636</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1182114208782745</v>
+        <v>0.1191418918882207</v>
       </c>
       <c r="T37">
-        <v>1.6723191888747</v>
+        <v>1.693808126748747</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.889764900023973</v>
+        <v>5.72616031946775</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09119375560846125</v>
+        <v>0.09102222464604409</v>
       </c>
       <c r="C38">
-        <v>345.3493261779738</v>
+        <v>340.3461185061088</v>
       </c>
       <c r="D38">
-        <v>397.6293261779739</v>
+        <v>398.1811185061088</v>
       </c>
       <c r="E38">
-        <v>-136.82</v>
+        <v>-131.265</v>
       </c>
       <c r="F38">
-        <v>199.98</v>
+        <v>205.535</v>
       </c>
       <c r="G38">
         <v>147.7</v>
@@ -4391,28 +4391,28 @@
         <v>63.325</v>
       </c>
       <c r="M38">
-        <v>11.058894</v>
+        <v>11.3660855</v>
       </c>
       <c r="N38">
-        <v>52.266106</v>
+        <v>51.95891450000001</v>
       </c>
       <c r="O38">
-        <v>13.0351668364</v>
+        <v>12.9585532763</v>
       </c>
       <c r="P38">
-        <v>39.2309391636</v>
+        <v>39.0003612237</v>
       </c>
       <c r="Q38">
-        <v>75.5309391636</v>
+        <v>75.30036122370001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1191418918882207</v>
+        <v>0.1201019016603875</v>
       </c>
       <c r="T38">
-        <v>1.693808126748747</v>
+        <v>1.715979253126731</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.726160319467751</v>
+        <v>5.571399229752407</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09102222464604409</v>
+        <v>0.09085069368362693</v>
       </c>
       <c r="C39">
-        <v>340.3461185061088</v>
+        <v>335.3444444126882</v>
       </c>
       <c r="D39">
-        <v>398.1811185061088</v>
+        <v>398.7344444126883</v>
       </c>
       <c r="E39">
-        <v>-131.265</v>
+        <v>-125.71</v>
       </c>
       <c r="F39">
-        <v>205.535</v>
+        <v>211.09</v>
       </c>
       <c r="G39">
         <v>147.7</v>
@@ -4473,28 +4473,28 @@
         <v>63.325</v>
       </c>
       <c r="M39">
-        <v>11.3660855</v>
+        <v>11.673277</v>
       </c>
       <c r="N39">
-        <v>51.95891450000001</v>
+        <v>51.651723</v>
       </c>
       <c r="O39">
-        <v>12.9585532763</v>
+        <v>12.8819397162</v>
       </c>
       <c r="P39">
-        <v>39.0003612237</v>
+        <v>38.7697832838</v>
       </c>
       <c r="Q39">
-        <v>75.30036122370001</v>
+        <v>75.06978328380001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1201019016603875</v>
+        <v>0.1210928794897209</v>
       </c>
       <c r="T39">
-        <v>1.715979253126731</v>
+        <v>1.738865577129812</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.571399229752407</v>
+        <v>5.424783460548396</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09085069368362693</v>
+        <v>0.09067916272120977</v>
       </c>
       <c r="C40">
-        <v>335.3444444126882</v>
+        <v>330.3443102999462</v>
       </c>
       <c r="D40">
-        <v>398.7344444126883</v>
+        <v>399.2893102999462</v>
       </c>
       <c r="E40">
-        <v>-125.71</v>
+        <v>-120.155</v>
       </c>
       <c r="F40">
-        <v>211.09</v>
+        <v>216.645</v>
       </c>
       <c r="G40">
         <v>147.7</v>
@@ -4555,28 +4555,28 @@
         <v>63.325</v>
       </c>
       <c r="M40">
-        <v>11.673277</v>
+        <v>11.9804685</v>
       </c>
       <c r="N40">
-        <v>51.651723</v>
+        <v>51.3445315</v>
       </c>
       <c r="O40">
-        <v>12.8819397162</v>
+        <v>12.8053261561</v>
       </c>
       <c r="P40">
-        <v>38.7697832838</v>
+        <v>38.5392053439</v>
       </c>
       <c r="Q40">
-        <v>75.06978328380001</v>
+        <v>74.83920534390001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1210928794897209</v>
+        <v>0.1221163483954258</v>
       </c>
       <c r="T40">
-        <v>1.738865577129812</v>
+        <v>1.762502272411683</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.424783460548396</v>
+        <v>5.285686448739463</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09067916272120977</v>
+        <v>0.0905076317587926</v>
       </c>
       <c r="C41">
-        <v>330.3443102999462</v>
+        <v>325.3457226058023</v>
       </c>
       <c r="D41">
-        <v>399.2893102999462</v>
+        <v>399.8457226058023</v>
       </c>
       <c r="E41">
-        <v>-120.155</v>
+        <v>-114.6</v>
       </c>
       <c r="F41">
-        <v>216.645</v>
+        <v>222.2</v>
       </c>
       <c r="G41">
         <v>147.7</v>
@@ -4637,28 +4637,28 @@
         <v>63.325</v>
       </c>
       <c r="M41">
-        <v>11.9804685</v>
+        <v>12.28766</v>
       </c>
       <c r="N41">
-        <v>51.3445315</v>
+        <v>51.03734</v>
       </c>
       <c r="O41">
-        <v>12.8053261561</v>
+        <v>12.728712596</v>
       </c>
       <c r="P41">
-        <v>38.5392053439</v>
+        <v>38.308627404</v>
       </c>
       <c r="Q41">
-        <v>74.83920534390001</v>
+        <v>74.608627404</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1221163483954258</v>
+        <v>0.123173932931321</v>
       </c>
       <c r="T41">
-        <v>1.762502272411683</v>
+        <v>1.786926857536282</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.285686448739463</v>
+        <v>5.153544287520976</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0905076317587926</v>
+        <v>0.09033610079637544</v>
       </c>
       <c r="C42">
-        <v>325.3457226058023</v>
+        <v>320.3486878041118</v>
       </c>
       <c r="D42">
-        <v>399.8457226058023</v>
+        <v>400.4036878041119</v>
       </c>
       <c r="E42">
-        <v>-114.6</v>
+        <v>-109.045</v>
       </c>
       <c r="F42">
-        <v>222.2</v>
+        <v>227.755</v>
       </c>
       <c r="G42">
         <v>147.7</v>
@@ -4719,28 +4719,28 @@
         <v>63.325</v>
       </c>
       <c r="M42">
-        <v>12.28766</v>
+        <v>12.5948515</v>
       </c>
       <c r="N42">
-        <v>51.03734</v>
+        <v>50.7301485</v>
       </c>
       <c r="O42">
-        <v>12.728712596</v>
+        <v>12.6520990359</v>
       </c>
       <c r="P42">
-        <v>38.308627404</v>
+        <v>38.0780494641</v>
       </c>
       <c r="Q42">
-        <v>74.608627404</v>
+        <v>74.3780494641</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.123173932931321</v>
+        <v>0.1242673677904668</v>
       </c>
       <c r="T42">
-        <v>1.786926857536282</v>
+        <v>1.812179394699004</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.153544287520976</v>
+        <v>5.027848085386317</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09033610079637544</v>
+        <v>0.09016456983395826</v>
       </c>
       <c r="C43">
-        <v>320.3486878041118</v>
+        <v>315.3532124049162</v>
       </c>
       <c r="D43">
-        <v>400.4036878041119</v>
+        <v>400.9632124049163</v>
       </c>
       <c r="E43">
-        <v>-109.045</v>
+        <v>-103.49</v>
       </c>
       <c r="F43">
-        <v>227.755</v>
+        <v>233.31</v>
       </c>
       <c r="G43">
         <v>147.7</v>
@@ -4801,28 +4801,28 @@
         <v>63.325</v>
       </c>
       <c r="M43">
-        <v>12.5948515</v>
+        <v>12.902043</v>
       </c>
       <c r="N43">
-        <v>50.7301485</v>
+        <v>50.422957</v>
       </c>
       <c r="O43">
-        <v>12.6520990359</v>
+        <v>12.5754854758</v>
       </c>
       <c r="P43">
-        <v>38.0780494641</v>
+        <v>37.8474715242</v>
       </c>
       <c r="Q43">
-        <v>74.3780494641</v>
+        <v>74.1474715242</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1242673677904668</v>
+        <v>0.125398507299928</v>
       </c>
       <c r="T43">
-        <v>1.812179394699004</v>
+        <v>1.838302709005267</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.027848085386317</v>
+        <v>4.908137416686642</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09016456983395826</v>
+        <v>0.08999303887154111</v>
       </c>
       <c r="C44">
-        <v>315.3532124049163</v>
+        <v>310.3593029546962</v>
       </c>
       <c r="D44">
-        <v>400.9632124049163</v>
+        <v>401.5243029546963</v>
       </c>
       <c r="E44">
-        <v>-103.49</v>
+        <v>-97.935</v>
       </c>
       <c r="F44">
-        <v>233.31</v>
+        <v>238.865</v>
       </c>
       <c r="G44">
         <v>147.7</v>
@@ -4883,28 +4883,28 @@
         <v>63.325</v>
       </c>
       <c r="M44">
-        <v>12.902043</v>
+        <v>13.2092345</v>
       </c>
       <c r="N44">
-        <v>50.422957</v>
+        <v>50.1157655</v>
       </c>
       <c r="O44">
-        <v>12.5754854758</v>
+        <v>12.4988719157</v>
       </c>
       <c r="P44">
-        <v>37.8474715242</v>
+        <v>37.6168935843</v>
       </c>
       <c r="Q44">
-        <v>74.1474715242</v>
+        <v>73.9168935843</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.125398507299928</v>
+        <v>0.1265693359149844</v>
       </c>
       <c r="T44">
-        <v>1.838302709005267</v>
+        <v>1.865342630831049</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.908137416686644</v>
+        <v>4.793994686066025</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08999303887154111</v>
+        <v>0.08982150790912394</v>
       </c>
       <c r="C45">
-        <v>310.3593029546962</v>
+        <v>305.3669660366278</v>
       </c>
       <c r="D45">
-        <v>401.5243029546963</v>
+        <v>402.0869660366278</v>
       </c>
       <c r="E45">
-        <v>-97.935</v>
+        <v>-92.38000000000002</v>
       </c>
       <c r="F45">
-        <v>238.865</v>
+        <v>244.42</v>
       </c>
       <c r="G45">
         <v>147.7</v>
@@ -4965,28 +4965,28 @@
         <v>63.325</v>
       </c>
       <c r="M45">
-        <v>13.2092345</v>
+        <v>13.516426</v>
       </c>
       <c r="N45">
-        <v>50.1157655</v>
+        <v>49.80857400000001</v>
       </c>
       <c r="O45">
-        <v>12.4988719157</v>
+        <v>12.4222583556</v>
       </c>
       <c r="P45">
-        <v>37.6168935843</v>
+        <v>37.38631564440001</v>
       </c>
       <c r="Q45">
-        <v>73.9168935843</v>
+        <v>73.6863156444</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1265693359149844</v>
+        <v>0.1277819798377213</v>
       </c>
       <c r="T45">
-        <v>1.865342630831049</v>
+        <v>1.893348264150608</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.793994686066025</v>
+        <v>4.685040261382706</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08982150790912394</v>
+        <v>0.08964997694670679</v>
       </c>
       <c r="C46">
-        <v>305.3669660366278</v>
+        <v>300.3762082708387</v>
       </c>
       <c r="D46">
-        <v>402.0869660366278</v>
+        <v>402.6512082708387</v>
       </c>
       <c r="E46">
-        <v>-92.38000000000002</v>
+        <v>-86.82500000000002</v>
       </c>
       <c r="F46">
-        <v>244.42</v>
+        <v>249.975</v>
       </c>
       <c r="G46">
         <v>147.7</v>
@@ -5047,28 +5047,28 @@
         <v>63.325</v>
       </c>
       <c r="M46">
-        <v>13.516426</v>
+        <v>13.8236175</v>
       </c>
       <c r="N46">
-        <v>49.80857400000001</v>
+        <v>49.50138250000001</v>
       </c>
       <c r="O46">
-        <v>12.4222583556</v>
+        <v>12.3456447955</v>
       </c>
       <c r="P46">
-        <v>37.38631564440001</v>
+        <v>37.15573770450001</v>
       </c>
       <c r="Q46">
-        <v>73.6863156444</v>
+        <v>73.4557377045</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1277819798377213</v>
+        <v>0.1290387199031032</v>
       </c>
       <c r="T46">
-        <v>1.893348264150608</v>
+        <v>1.922372284136334</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.685040261382706</v>
+        <v>4.580928255574202</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08964997694670679</v>
+        <v>0.09034163598428961</v>
       </c>
       <c r="C47">
-        <v>300.3762082708387</v>
+        <v>292.5556583318353</v>
       </c>
       <c r="D47">
-        <v>402.6512082708387</v>
+        <v>400.3856583318353</v>
       </c>
       <c r="E47">
-        <v>-86.82500000000002</v>
+        <v>-81.27000000000001</v>
       </c>
       <c r="F47">
-        <v>249.975</v>
+        <v>255.53</v>
       </c>
       <c r="G47">
         <v>147.7</v>
@@ -5129,45 +5129,45 @@
         <v>63.325</v>
       </c>
       <c r="M47">
-        <v>13.8236175</v>
+        <v>14.769634</v>
       </c>
       <c r="N47">
-        <v>49.50138250000001</v>
+        <v>48.555366</v>
       </c>
       <c r="O47">
-        <v>12.3456447955</v>
+        <v>12.1097082804</v>
       </c>
       <c r="P47">
-        <v>37.15573770450001</v>
+        <v>36.4456577196</v>
       </c>
       <c r="Q47">
-        <v>73.4557377045</v>
+        <v>72.74565771959999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1290387199031032</v>
+        <v>0.1303420058968326</v>
       </c>
       <c r="T47">
-        <v>1.922372284136334</v>
+        <v>1.952471267825234</v>
       </c>
       <c r="U47">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V47">
         <v>0.2494</v>
       </c>
       <c r="W47">
-        <v>0.04150818</v>
+        <v>0.04338468</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.580928255574202</v>
+        <v>4.287513150292011</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09034163598428961</v>
+        <v>0.09018887002187245</v>
       </c>
       <c r="C48">
-        <v>292.5556583318353</v>
+        <v>287.4988514678485</v>
       </c>
       <c r="D48">
-        <v>400.3856583318353</v>
+        <v>400.8838514678486</v>
       </c>
       <c r="E48">
-        <v>-81.27000000000001</v>
+        <v>-75.71499999999997</v>
       </c>
       <c r="F48">
-        <v>255.53</v>
+        <v>261.085</v>
       </c>
       <c r="G48">
         <v>147.7</v>
@@ -5211,28 +5211,28 @@
         <v>63.325</v>
       </c>
       <c r="M48">
-        <v>14.769634</v>
+        <v>15.090713</v>
       </c>
       <c r="N48">
-        <v>48.555366</v>
+        <v>48.234287</v>
       </c>
       <c r="O48">
-        <v>12.1097082804</v>
+        <v>12.0296311778</v>
       </c>
       <c r="P48">
-        <v>36.4456577196</v>
+        <v>36.2046558222</v>
       </c>
       <c r="Q48">
-        <v>72.74565771959999</v>
+        <v>72.50465582219999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1303420058968326</v>
+        <v>0.131694472494099</v>
       </c>
       <c r="T48">
-        <v>1.952471267825234</v>
+        <v>1.983706062219376</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.287513150292011</v>
+        <v>4.196289466243245</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09018887002187245</v>
+        <v>0.09003610405945529</v>
       </c>
       <c r="C49">
-        <v>287.4988514678485</v>
+        <v>282.4432859350982</v>
       </c>
       <c r="D49">
-        <v>400.8838514678486</v>
+        <v>401.3832859350982</v>
       </c>
       <c r="E49">
-        <v>-75.71499999999997</v>
+        <v>-70.15999999999997</v>
       </c>
       <c r="F49">
-        <v>261.085</v>
+        <v>266.64</v>
       </c>
       <c r="G49">
         <v>147.7</v>
@@ -5293,28 +5293,28 @@
         <v>63.325</v>
       </c>
       <c r="M49">
-        <v>15.090713</v>
+        <v>15.411792</v>
       </c>
       <c r="N49">
-        <v>48.234287</v>
+        <v>47.913208</v>
       </c>
       <c r="O49">
-        <v>12.0296311778</v>
+        <v>11.9495540752</v>
       </c>
       <c r="P49">
-        <v>36.2046558222</v>
+        <v>35.9636539248</v>
       </c>
       <c r="Q49">
-        <v>72.50465582219999</v>
+        <v>72.2636539248</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.131694472494099</v>
+        <v>0.133098957037414</v>
       </c>
       <c r="T49">
-        <v>1.983706062219376</v>
+        <v>2.016142194859446</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.196289466243245</v>
+        <v>4.108866769029843</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09003610405945528</v>
+        <v>0.08988333809703811</v>
       </c>
       <c r="C50">
-        <v>282.4432859350983</v>
+        <v>277.388966378847</v>
       </c>
       <c r="D50">
-        <v>401.3832859350983</v>
+        <v>401.8839663788469</v>
       </c>
       <c r="E50">
-        <v>-70.16000000000003</v>
+        <v>-64.60500000000002</v>
       </c>
       <c r="F50">
-        <v>266.64</v>
+        <v>272.195</v>
       </c>
       <c r="G50">
         <v>147.7</v>
@@ -5375,28 +5375,28 @@
         <v>63.325</v>
       </c>
       <c r="M50">
-        <v>15.411792</v>
+        <v>15.732871</v>
       </c>
       <c r="N50">
-        <v>47.913208</v>
+        <v>47.592129</v>
       </c>
       <c r="O50">
-        <v>11.9495540752</v>
+        <v>11.8694769726</v>
       </c>
       <c r="P50">
-        <v>35.9636539248</v>
+        <v>35.7226520274</v>
       </c>
       <c r="Q50">
-        <v>72.2636539248</v>
+        <v>72.0226520274</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.133098957037414</v>
+        <v>0.1345585194059571</v>
       </c>
       <c r="T50">
-        <v>2.016142194859446</v>
+        <v>2.049850332701088</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.108866769029845</v>
+        <v>4.025012345172092</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08988333809703811</v>
+        <v>0.09104412213462094</v>
       </c>
       <c r="C51">
-        <v>277.388966378847</v>
+        <v>268.0605919353956</v>
       </c>
       <c r="D51">
-        <v>401.8839663788469</v>
+        <v>398.1105919353956</v>
       </c>
       <c r="E51">
-        <v>-64.60500000000002</v>
+        <v>-59.05000000000001</v>
       </c>
       <c r="F51">
-        <v>272.195</v>
+        <v>277.75</v>
       </c>
       <c r="G51">
         <v>147.7</v>
@@ -5457,45 +5457,45 @@
         <v>63.325</v>
       </c>
       <c r="M51">
-        <v>15.732871</v>
+        <v>17.026075</v>
       </c>
       <c r="N51">
-        <v>47.592129</v>
+        <v>46.298925</v>
       </c>
       <c r="O51">
-        <v>11.8694769726</v>
+        <v>11.546951895</v>
       </c>
       <c r="P51">
-        <v>35.7226520274</v>
+        <v>34.751973105</v>
       </c>
       <c r="Q51">
-        <v>72.0226520274</v>
+        <v>71.051973105</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1345585194059571</v>
+        <v>0.1360764642692419</v>
       </c>
       <c r="T51">
-        <v>2.049850332701088</v>
+        <v>2.084906796056395</v>
       </c>
       <c r="U51">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V51">
         <v>0.2494</v>
       </c>
       <c r="W51">
-        <v>0.04338468</v>
+        <v>0.04601178</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>4.025012345172092</v>
+        <v>3.719295257421338</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09104412213462094</v>
+        <v>0.09091762717220378</v>
       </c>
       <c r="C52">
-        <v>268.0605919353956</v>
+        <v>262.9133469841639</v>
       </c>
       <c r="D52">
-        <v>398.1105919353956</v>
+        <v>398.5183469841639</v>
       </c>
       <c r="E52">
-        <v>-59.05000000000001</v>
+        <v>-53.495</v>
       </c>
       <c r="F52">
-        <v>277.75</v>
+        <v>283.305</v>
       </c>
       <c r="G52">
         <v>147.7</v>
@@ -5539,28 +5539,28 @@
         <v>63.325</v>
       </c>
       <c r="M52">
-        <v>17.026075</v>
+        <v>17.3665965</v>
       </c>
       <c r="N52">
-        <v>46.298925</v>
+        <v>45.9584035</v>
       </c>
       <c r="O52">
-        <v>11.546951895</v>
+        <v>11.4620258329</v>
       </c>
       <c r="P52">
-        <v>34.751973105</v>
+        <v>34.4963776671</v>
       </c>
       <c r="Q52">
-        <v>71.051973105</v>
+        <v>70.79637766709999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1360764642692419</v>
+        <v>0.137656366065722</v>
       </c>
       <c r="T52">
-        <v>2.084906796056395</v>
+        <v>2.121394135467022</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.719295257421338</v>
+        <v>3.646367899432684</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09091762717220378</v>
+        <v>0.09079113220978662</v>
       </c>
       <c r="C53">
-        <v>262.9133469841639</v>
+        <v>257.7669381556067</v>
       </c>
       <c r="D53">
-        <v>398.5183469841639</v>
+        <v>398.9269381556068</v>
       </c>
       <c r="E53">
-        <v>-53.495</v>
+        <v>-47.94</v>
       </c>
       <c r="F53">
-        <v>283.305</v>
+        <v>288.86</v>
       </c>
       <c r="G53">
         <v>147.7</v>
@@ -5621,28 +5621,28 @@
         <v>63.325</v>
       </c>
       <c r="M53">
-        <v>17.3665965</v>
+        <v>17.707118</v>
       </c>
       <c r="N53">
-        <v>45.9584035</v>
+        <v>45.617882</v>
       </c>
       <c r="O53">
-        <v>11.4620258329</v>
+        <v>11.3770997708</v>
       </c>
       <c r="P53">
-        <v>34.4963776671</v>
+        <v>34.2407822292</v>
       </c>
       <c r="Q53">
-        <v>70.79637766709999</v>
+        <v>70.5407822292</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.137656366065722</v>
+        <v>0.1393020971037221</v>
       </c>
       <c r="T53">
-        <v>2.121394135467022</v>
+        <v>2.159401780686424</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.646367899432684</v>
+        <v>3.576245439828209</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09079113220978662</v>
+        <v>0.09066463724736945</v>
       </c>
       <c r="C54">
-        <v>257.7669381556067</v>
+        <v>252.6213680241321</v>
       </c>
       <c r="D54">
-        <v>398.9269381556068</v>
+        <v>399.3363680241322</v>
       </c>
       <c r="E54">
-        <v>-47.94</v>
+        <v>-42.38499999999999</v>
       </c>
       <c r="F54">
-        <v>288.86</v>
+        <v>294.415</v>
       </c>
       <c r="G54">
         <v>147.7</v>
@@ -5703,28 +5703,28 @@
         <v>63.325</v>
       </c>
       <c r="M54">
-        <v>17.707118</v>
+        <v>18.0476395</v>
       </c>
       <c r="N54">
-        <v>45.617882</v>
+        <v>45.2773605</v>
       </c>
       <c r="O54">
-        <v>11.3770997708</v>
+        <v>11.2921737087</v>
       </c>
       <c r="P54">
-        <v>34.2407822292</v>
+        <v>33.9851867913</v>
       </c>
       <c r="Q54">
-        <v>70.5407822292</v>
+        <v>70.28518679129999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1393020971037221</v>
+        <v>0.1410178592497223</v>
       </c>
       <c r="T54">
-        <v>2.159401780686424</v>
+        <v>2.199026772510907</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.576245439828209</v>
+        <v>3.508769110774846</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09066463724736945</v>
+        <v>0.09167304948495228</v>
       </c>
       <c r="C55">
-        <v>252.6213680241321</v>
+        <v>243.8255769938414</v>
       </c>
       <c r="D55">
-        <v>399.3363680241322</v>
+        <v>396.0955769938415</v>
       </c>
       <c r="E55">
-        <v>-42.38499999999999</v>
+        <v>-36.82999999999998</v>
       </c>
       <c r="F55">
-        <v>294.415</v>
+        <v>299.97</v>
       </c>
       <c r="G55">
         <v>147.7</v>
@@ -5785,45 +5785,45 @@
         <v>63.325</v>
       </c>
       <c r="M55">
-        <v>18.0476395</v>
+        <v>19.228077</v>
       </c>
       <c r="N55">
-        <v>45.2773605</v>
+        <v>44.096923</v>
       </c>
       <c r="O55">
-        <v>11.2921737087</v>
+        <v>10.9977725962</v>
       </c>
       <c r="P55">
-        <v>33.9851867913</v>
+        <v>33.0991504038</v>
       </c>
       <c r="Q55">
-        <v>70.28518679129999</v>
+        <v>69.39915040380001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1410178592497223</v>
+        <v>0.1428082197498963</v>
       </c>
       <c r="T55">
-        <v>2.199026772510907</v>
+        <v>2.240374590066889</v>
       </c>
       <c r="U55">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V55">
         <v>0.2494</v>
       </c>
       <c r="W55">
-        <v>0.04601178</v>
+        <v>0.04811346</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.508769110774846</v>
+        <v>3.293361057374588</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09167304948495228</v>
+        <v>0.09156757132253512</v>
       </c>
       <c r="C56">
-        <v>243.8255769938414</v>
+        <v>238.6070927608205</v>
       </c>
       <c r="D56">
-        <v>396.0955769938415</v>
+        <v>396.4320927608205</v>
       </c>
       <c r="E56">
-        <v>-36.82999999999998</v>
+        <v>-31.27499999999998</v>
       </c>
       <c r="F56">
-        <v>299.97</v>
+        <v>305.525</v>
       </c>
       <c r="G56">
         <v>147.7</v>
@@ -5867,28 +5867,28 @@
         <v>63.325</v>
       </c>
       <c r="M56">
-        <v>19.228077</v>
+        <v>19.5841525</v>
       </c>
       <c r="N56">
-        <v>44.096923</v>
+        <v>43.7408475</v>
       </c>
       <c r="O56">
-        <v>10.9977725962</v>
+        <v>10.9089673665</v>
       </c>
       <c r="P56">
-        <v>33.0991504038</v>
+        <v>32.8318801335</v>
       </c>
       <c r="Q56">
-        <v>69.39915040380001</v>
+        <v>69.1318801335</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1428082197498963</v>
+        <v>0.1446781518278558</v>
       </c>
       <c r="T56">
-        <v>2.240374590066889</v>
+        <v>2.283560088403138</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.293361057374588</v>
+        <v>3.233481765422323</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09156757132253512</v>
+        <v>0.09146209316011795</v>
       </c>
       <c r="C57">
-        <v>238.6070927608205</v>
+        <v>233.3891808096374</v>
       </c>
       <c r="D57">
-        <v>396.4320927608205</v>
+        <v>396.7691808096374</v>
       </c>
       <c r="E57">
-        <v>-31.27499999999998</v>
+        <v>-25.71999999999997</v>
       </c>
       <c r="F57">
-        <v>305.525</v>
+        <v>311.08</v>
       </c>
       <c r="G57">
         <v>147.7</v>
@@ -5949,28 +5949,28 @@
         <v>63.325</v>
       </c>
       <c r="M57">
-        <v>19.5841525</v>
+        <v>19.940228</v>
       </c>
       <c r="N57">
-        <v>43.7408475</v>
+        <v>43.384772</v>
       </c>
       <c r="O57">
-        <v>10.9089673665</v>
+        <v>10.8201621368</v>
       </c>
       <c r="P57">
-        <v>32.8318801335</v>
+        <v>32.5646098632</v>
       </c>
       <c r="Q57">
-        <v>69.1318801335</v>
+        <v>68.8646098632</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1446781518278558</v>
+        <v>0.1466330808184499</v>
       </c>
       <c r="T57">
-        <v>2.283560088403138</v>
+        <v>2.328708563936488</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.233481765422323</v>
+        <v>3.175741019611209</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09146209316011795</v>
+        <v>0.09135661499770079</v>
       </c>
       <c r="C58">
-        <v>233.3891808096374</v>
+        <v>228.171842601376</v>
       </c>
       <c r="D58">
-        <v>396.7691808096374</v>
+        <v>397.1068426013761</v>
       </c>
       <c r="E58">
-        <v>-25.71999999999997</v>
+        <v>-20.16499999999996</v>
       </c>
       <c r="F58">
-        <v>311.08</v>
+        <v>316.635</v>
       </c>
       <c r="G58">
         <v>147.7</v>
@@ -6031,28 +6031,28 @@
         <v>63.325</v>
       </c>
       <c r="M58">
-        <v>19.940228</v>
+        <v>20.2963035</v>
       </c>
       <c r="N58">
-        <v>43.384772</v>
+        <v>43.0286965</v>
       </c>
       <c r="O58">
-        <v>10.8201621368</v>
+        <v>10.7313569071</v>
       </c>
       <c r="P58">
-        <v>32.5646098632</v>
+        <v>32.29733959289999</v>
       </c>
       <c r="Q58">
-        <v>68.8646098632</v>
+        <v>68.5973395929</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1466330808184499</v>
+        <v>0.1486789367388391</v>
       </c>
       <c r="T58">
-        <v>2.328708563936488</v>
+        <v>2.375956968564413</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.175741019611209</v>
+        <v>3.120026264881188</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09135661499770079</v>
+        <v>0.09125113683528362</v>
       </c>
       <c r="C59">
-        <v>228.171842601376</v>
+        <v>222.9550796020984</v>
       </c>
       <c r="D59">
-        <v>397.1068426013761</v>
+        <v>397.4450796020985</v>
       </c>
       <c r="E59">
-        <v>-20.16499999999996</v>
+        <v>-14.60999999999996</v>
       </c>
       <c r="F59">
-        <v>316.635</v>
+        <v>322.1900000000001</v>
       </c>
       <c r="G59">
         <v>147.7</v>
@@ -6113,28 +6113,28 @@
         <v>63.325</v>
       </c>
       <c r="M59">
-        <v>20.2963035</v>
+        <v>20.652379</v>
       </c>
       <c r="N59">
-        <v>43.0286965</v>
+        <v>42.672621</v>
       </c>
       <c r="O59">
-        <v>10.7313569071</v>
+        <v>10.6425516774</v>
       </c>
       <c r="P59">
-        <v>32.29733959289999</v>
+        <v>32.0300693226</v>
       </c>
       <c r="Q59">
-        <v>68.5973395929</v>
+        <v>68.3300693226</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1486789367388391</v>
+        <v>0.1508222143697229</v>
       </c>
       <c r="T59">
-        <v>2.375956968564413</v>
+        <v>2.425455297222239</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.120026264881188</v>
+        <v>3.066232708590134</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09125113683528363</v>
+        <v>0.09114565867286648</v>
       </c>
       <c r="C60">
-        <v>222.9550796020985</v>
+        <v>217.7388932828658</v>
       </c>
       <c r="D60">
-        <v>397.4450796020985</v>
+        <v>397.7838932828658</v>
       </c>
       <c r="E60">
-        <v>-14.61000000000001</v>
+        <v>-9.055000000000007</v>
       </c>
       <c r="F60">
-        <v>322.19</v>
+        <v>327.745</v>
       </c>
       <c r="G60">
         <v>147.7</v>
@@ -6195,28 +6195,28 @@
         <v>63.325</v>
       </c>
       <c r="M60">
-        <v>20.652379</v>
+        <v>21.0084545</v>
       </c>
       <c r="N60">
-        <v>42.67262100000001</v>
+        <v>42.3165455</v>
       </c>
       <c r="O60">
-        <v>10.6425516774</v>
+        <v>10.5537464477</v>
       </c>
       <c r="P60">
-        <v>32.03006932260001</v>
+        <v>31.7627990523</v>
       </c>
       <c r="Q60">
-        <v>68.3300693226</v>
+        <v>68.06279905229999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1508222143697229</v>
+        <v>0.1530700421289426</v>
       </c>
       <c r="T60">
-        <v>2.425455297222239</v>
+        <v>2.47736817849752</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.066232708590134</v>
+        <v>3.014262662681826</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09114565867286648</v>
+        <v>0.0945529885104493</v>
       </c>
       <c r="C61">
-        <v>217.7388932828658</v>
+        <v>201.5232194672628</v>
       </c>
       <c r="D61">
-        <v>397.7838932828658</v>
+        <v>387.1232194672629</v>
       </c>
       <c r="E61">
-        <v>-9.055000000000007</v>
+        <v>-3.5</v>
       </c>
       <c r="F61">
-        <v>327.745</v>
+        <v>333.3</v>
       </c>
       <c r="G61">
         <v>147.7</v>
@@ -6277,45 +6277,45 @@
         <v>63.325</v>
       </c>
       <c r="M61">
-        <v>21.0084545</v>
+        <v>23.96427</v>
       </c>
       <c r="N61">
-        <v>42.3165455</v>
+        <v>39.36073</v>
       </c>
       <c r="O61">
-        <v>10.5537464477</v>
+        <v>9.816566062000001</v>
       </c>
       <c r="P61">
-        <v>31.7627990523</v>
+        <v>29.544163938</v>
       </c>
       <c r="Q61">
-        <v>68.06279905229999</v>
+        <v>65.84416393800001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1530700421289426</v>
+        <v>0.1554302612761232</v>
       </c>
       <c r="T61">
-        <v>2.47736817849752</v>
+        <v>2.531876703836565</v>
       </c>
       <c r="U61">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V61">
         <v>0.2494</v>
       </c>
       <c r="W61">
-        <v>0.04811346</v>
+        <v>0.05396814</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>3.014262662681826</v>
+        <v>2.642475652294019</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.0945529885104493</v>
+        <v>0.09450605714803213</v>
       </c>
       <c r="C62">
-        <v>201.5232194672628</v>
+        <v>196.1111733683019</v>
       </c>
       <c r="D62">
-        <v>387.1232194672629</v>
+        <v>387.266173368302</v>
       </c>
       <c r="E62">
-        <v>-3.5</v>
+        <v>2.055000000000007</v>
       </c>
       <c r="F62">
-        <v>333.3</v>
+        <v>338.855</v>
       </c>
       <c r="G62">
         <v>147.7</v>
@@ -6359,28 +6359,28 @@
         <v>63.325</v>
       </c>
       <c r="M62">
-        <v>23.96427</v>
+        <v>24.3636745</v>
       </c>
       <c r="N62">
-        <v>39.36073</v>
+        <v>38.9613255</v>
       </c>
       <c r="O62">
-        <v>9.816566062000001</v>
+        <v>9.716954579700001</v>
       </c>
       <c r="P62">
-        <v>29.544163938</v>
+        <v>29.2443709203</v>
       </c>
       <c r="Q62">
-        <v>65.84416393800001</v>
+        <v>65.5443709203</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1554302612761232</v>
+        <v>0.1579115173026465</v>
       </c>
       <c r="T62">
-        <v>2.531876703836565</v>
+        <v>2.589180538167356</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.642475652294019</v>
+        <v>2.599156379305593</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09450605714803213</v>
+        <v>0.09445912578561497</v>
       </c>
       <c r="C63">
-        <v>196.1111733683019</v>
+        <v>190.6992328861884</v>
       </c>
       <c r="D63">
-        <v>387.266173368302</v>
+        <v>387.4092328861884</v>
       </c>
       <c r="E63">
-        <v>2.055000000000007</v>
+        <v>7.610000000000014</v>
       </c>
       <c r="F63">
-        <v>338.855</v>
+        <v>344.41</v>
       </c>
       <c r="G63">
         <v>147.7</v>
@@ -6441,28 +6441,28 @@
         <v>63.325</v>
       </c>
       <c r="M63">
-        <v>24.3636745</v>
+        <v>24.763079</v>
       </c>
       <c r="N63">
-        <v>38.9613255</v>
+        <v>38.561921</v>
       </c>
       <c r="O63">
-        <v>9.716954579700001</v>
+        <v>9.617343097399999</v>
       </c>
       <c r="P63">
-        <v>29.2443709203</v>
+        <v>28.9445779026</v>
       </c>
       <c r="Q63">
-        <v>65.5443709203</v>
+        <v>65.2445779026</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1579115173026465</v>
+        <v>0.1605233657516184</v>
       </c>
       <c r="T63">
-        <v>2.589180538167356</v>
+        <v>2.649500363778715</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.599156379305593</v>
+        <v>2.557234502220019</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09445912578561497</v>
+        <v>0.09441219442319781</v>
       </c>
       <c r="C64">
-        <v>190.6992328861884</v>
+        <v>185.287398138013</v>
       </c>
       <c r="D64">
-        <v>387.4092328861884</v>
+        <v>387.5523981380129</v>
       </c>
       <c r="E64">
-        <v>7.610000000000014</v>
+        <v>13.16499999999996</v>
       </c>
       <c r="F64">
-        <v>344.41</v>
+        <v>349.965</v>
       </c>
       <c r="G64">
         <v>147.7</v>
@@ -6523,28 +6523,28 @@
         <v>63.325</v>
       </c>
       <c r="M64">
-        <v>24.763079</v>
+        <v>25.1624835</v>
       </c>
       <c r="N64">
-        <v>38.561921</v>
+        <v>38.1625165</v>
       </c>
       <c r="O64">
-        <v>9.617343097399999</v>
+        <v>9.517731615100001</v>
       </c>
       <c r="P64">
-        <v>28.9445779026</v>
+        <v>28.6447848849</v>
       </c>
       <c r="Q64">
-        <v>65.2445779026</v>
+        <v>64.9447848849</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1605233657516184</v>
+        <v>0.1632763951978319</v>
       </c>
       <c r="T64">
-        <v>2.649500363778715</v>
+        <v>2.713080720504201</v>
       </c>
       <c r="U64">
         <v>0.07190000000000001</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.557234502220019</v>
+        <v>2.516643478375257</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09441219442319781</v>
+        <v>0.09623876066078063</v>
       </c>
       <c r="C65">
-        <v>185.287398138013</v>
+        <v>174.2373877150696</v>
       </c>
       <c r="D65">
-        <v>387.5523981380129</v>
+        <v>382.0573877150696</v>
       </c>
       <c r="E65">
-        <v>13.16499999999996</v>
+        <v>18.71999999999997</v>
       </c>
       <c r="F65">
-        <v>349.965</v>
+        <v>355.52</v>
       </c>
       <c r="G65">
         <v>147.7</v>
@@ -6605,45 +6605,45 @@
         <v>63.325</v>
       </c>
       <c r="M65">
-        <v>25.1624835</v>
+        <v>26.948416</v>
       </c>
       <c r="N65">
-        <v>38.1625165</v>
+        <v>36.376584</v>
       </c>
       <c r="O65">
-        <v>9.517731615100001</v>
+        <v>9.0723200496</v>
       </c>
       <c r="P65">
-        <v>28.6447848849</v>
+        <v>27.3042639504</v>
       </c>
       <c r="Q65">
-        <v>64.9447848849</v>
+        <v>63.6042639504</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1632763951978319</v>
+        <v>0.1661823707243907</v>
       </c>
       <c r="T65">
-        <v>2.713080720504201</v>
+        <v>2.780193319269993</v>
       </c>
       <c r="U65">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V65">
         <v>0.2494</v>
       </c>
       <c r="W65">
-        <v>0.05396814</v>
+        <v>0.05689548</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.516643478375257</v>
+        <v>2.349859821074456</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09623876066078063</v>
+        <v>0.09622110269836348</v>
       </c>
       <c r="C66">
-        <v>174.2373877150696</v>
+        <v>168.7347636018442</v>
       </c>
       <c r="D66">
-        <v>382.0573877150696</v>
+        <v>382.1097636018442</v>
       </c>
       <c r="E66">
-        <v>18.71999999999997</v>
+        <v>24.27499999999998</v>
       </c>
       <c r="F66">
-        <v>355.52</v>
+        <v>361.075</v>
       </c>
       <c r="G66">
         <v>147.7</v>
@@ -6687,28 +6687,28 @@
         <v>63.325</v>
       </c>
       <c r="M66">
-        <v>26.948416</v>
+        <v>27.369485</v>
       </c>
       <c r="N66">
-        <v>36.376584</v>
+        <v>35.95551500000001</v>
       </c>
       <c r="O66">
-        <v>9.0723200496</v>
+        <v>8.967305441000002</v>
       </c>
       <c r="P66">
-        <v>27.3042639504</v>
+        <v>26.988209559</v>
       </c>
       <c r="Q66">
-        <v>63.6042639504</v>
+        <v>63.288209559</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1661823707243907</v>
+        <v>0.1692544019953242</v>
       </c>
       <c r="T66">
-        <v>2.780193319269993</v>
+        <v>2.851140923679544</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.349859821074456</v>
+        <v>2.313708131519464</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09622110269836348</v>
+        <v>0.0962034447359463</v>
       </c>
       <c r="C67">
-        <v>168.7347636018442</v>
+        <v>163.2321538509096</v>
       </c>
       <c r="D67">
-        <v>382.1097636018442</v>
+        <v>382.1621538509097</v>
       </c>
       <c r="E67">
-        <v>24.27499999999998</v>
+        <v>29.82999999999998</v>
       </c>
       <c r="F67">
-        <v>361.075</v>
+        <v>366.63</v>
       </c>
       <c r="G67">
         <v>147.7</v>
@@ -6769,28 +6769,28 @@
         <v>63.325</v>
       </c>
       <c r="M67">
-        <v>27.369485</v>
+        <v>27.790554</v>
       </c>
       <c r="N67">
-        <v>35.95551500000001</v>
+        <v>35.534446</v>
       </c>
       <c r="O67">
-        <v>8.967305441000002</v>
+        <v>8.862290832400001</v>
       </c>
       <c r="P67">
-        <v>26.988209559</v>
+        <v>26.6721551676</v>
       </c>
       <c r="Q67">
-        <v>63.288209559</v>
+        <v>62.9721551676</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1692544019953242</v>
+        <v>0.1725071409880774</v>
       </c>
       <c r="T67">
-        <v>2.851140923679544</v>
+        <v>2.926261916583774</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.313708131519464</v>
+        <v>2.278651947708563</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.0962034447359463</v>
+        <v>0.09618578677352915</v>
       </c>
       <c r="C68">
-        <v>163.2321538509096</v>
+        <v>157.7295584681742</v>
       </c>
       <c r="D68">
-        <v>382.1621538509097</v>
+        <v>382.2145584681741</v>
       </c>
       <c r="E68">
-        <v>29.82999999999998</v>
+        <v>35.38499999999999</v>
       </c>
       <c r="F68">
-        <v>366.63</v>
+        <v>372.185</v>
       </c>
       <c r="G68">
         <v>147.7</v>
@@ -6851,28 +6851,28 @@
         <v>63.325</v>
       </c>
       <c r="M68">
-        <v>27.790554</v>
+        <v>28.211623</v>
       </c>
       <c r="N68">
-        <v>35.534446</v>
+        <v>35.113377</v>
       </c>
       <c r="O68">
-        <v>8.862290832400001</v>
+        <v>8.7572762238</v>
       </c>
       <c r="P68">
-        <v>26.6721551676</v>
+        <v>26.3561007762</v>
       </c>
       <c r="Q68">
-        <v>62.9721551676</v>
+        <v>62.6561007762</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1725071409880774</v>
+        <v>0.1759570156773611</v>
       </c>
       <c r="T68">
-        <v>2.926261916583774</v>
+        <v>3.005935696936746</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.278651947708563</v>
+        <v>2.244642217145748</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09618578677352915</v>
+        <v>0.09616812881111197</v>
       </c>
       <c r="C69">
-        <v>157.7295584681742</v>
+        <v>152.2269774595492</v>
       </c>
       <c r="D69">
-        <v>382.2145584681741</v>
+        <v>382.2669774595492</v>
       </c>
       <c r="E69">
-        <v>35.38499999999999</v>
+        <v>40.94</v>
       </c>
       <c r="F69">
-        <v>372.185</v>
+        <v>377.74</v>
       </c>
       <c r="G69">
         <v>147.7</v>
@@ -6933,28 +6933,28 @@
         <v>63.325</v>
       </c>
       <c r="M69">
-        <v>28.211623</v>
+        <v>28.632692</v>
       </c>
       <c r="N69">
-        <v>35.113377</v>
+        <v>34.692308</v>
       </c>
       <c r="O69">
-        <v>8.7572762238</v>
+        <v>8.6522616152</v>
       </c>
       <c r="P69">
-        <v>26.3561007762</v>
+        <v>26.0400463848</v>
       </c>
       <c r="Q69">
-        <v>62.6561007762</v>
+        <v>62.34004638479999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1759570156773611</v>
+        <v>0.1796225075347249</v>
       </c>
       <c r="T69">
-        <v>3.005935696936746</v>
+        <v>3.090589088561777</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.244642217145748</v>
+        <v>2.211632772775958</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09616812881111197</v>
+        <v>0.0961504708486948</v>
       </c>
       <c r="C70">
-        <v>152.2269774595492</v>
+        <v>146.7244108309499</v>
       </c>
       <c r="D70">
-        <v>382.2669774595492</v>
+        <v>382.3194108309499</v>
       </c>
       <c r="E70">
-        <v>40.94</v>
+        <v>46.495</v>
       </c>
       <c r="F70">
-        <v>377.74</v>
+        <v>383.295</v>
       </c>
       <c r="G70">
         <v>147.7</v>
@@ -7015,28 +7015,28 @@
         <v>63.325</v>
       </c>
       <c r="M70">
-        <v>28.632692</v>
+        <v>29.05376100000001</v>
       </c>
       <c r="N70">
-        <v>34.692308</v>
+        <v>34.27123899999999</v>
       </c>
       <c r="O70">
-        <v>8.6522616152</v>
+        <v>8.547247006599999</v>
       </c>
       <c r="P70">
-        <v>26.0400463848</v>
+        <v>25.72399199339999</v>
       </c>
       <c r="Q70">
-        <v>62.34004638479999</v>
+        <v>62.02399199339999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1796225075347249</v>
+        <v>0.1835244827377252</v>
       </c>
       <c r="T70">
-        <v>3.090589088561777</v>
+        <v>3.180703989323908</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.211632772775958</v>
+        <v>2.179580123895147</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0961504708486948</v>
+        <v>0.09613281288627765</v>
       </c>
       <c r="C71">
-        <v>146.7244108309499</v>
+        <v>141.221858588294</v>
       </c>
       <c r="D71">
-        <v>382.3194108309499</v>
+        <v>382.3718585882941</v>
       </c>
       <c r="E71">
-        <v>46.495</v>
+        <v>52.05000000000001</v>
       </c>
       <c r="F71">
-        <v>383.295</v>
+        <v>388.85</v>
       </c>
       <c r="G71">
         <v>147.7</v>
@@ -7097,28 +7097,28 @@
         <v>63.325</v>
       </c>
       <c r="M71">
-        <v>29.05376100000001</v>
+        <v>29.47483</v>
       </c>
       <c r="N71">
-        <v>34.27123899999999</v>
+        <v>33.85017</v>
       </c>
       <c r="O71">
-        <v>8.547247006599999</v>
+        <v>8.442232398</v>
       </c>
       <c r="P71">
-        <v>25.72399199339999</v>
+        <v>25.407937602</v>
       </c>
       <c r="Q71">
-        <v>62.02399199339999</v>
+        <v>61.70793760199999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1835244827377252</v>
+        <v>0.1876865896209255</v>
       </c>
       <c r="T71">
-        <v>3.180703989323908</v>
+        <v>3.276826550136848</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.179580123895147</v>
+        <v>2.148443264982359</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09613281288627765</v>
+        <v>0.0961151549238605</v>
       </c>
       <c r="C72">
-        <v>141.221858588294</v>
+        <v>135.7193207375031</v>
       </c>
       <c r="D72">
-        <v>382.3718585882941</v>
+        <v>382.4243207375031</v>
       </c>
       <c r="E72">
-        <v>52.05000000000001</v>
+        <v>57.60500000000002</v>
       </c>
       <c r="F72">
-        <v>388.85</v>
+        <v>394.405</v>
       </c>
       <c r="G72">
         <v>147.7</v>
@@ -7179,28 +7179,28 @@
         <v>63.325</v>
       </c>
       <c r="M72">
-        <v>29.47483</v>
+        <v>29.895899</v>
       </c>
       <c r="N72">
-        <v>33.85017</v>
+        <v>33.429101</v>
       </c>
       <c r="O72">
-        <v>8.442232398</v>
+        <v>8.3372177894</v>
       </c>
       <c r="P72">
-        <v>25.407937602</v>
+        <v>25.0918832106</v>
       </c>
       <c r="Q72">
-        <v>61.70793760199999</v>
+        <v>61.3918832106</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1876865896209255</v>
+        <v>0.1921357383581397</v>
       </c>
       <c r="T72">
-        <v>3.276826550136848</v>
+        <v>3.379578253074819</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.148443264982359</v>
+        <v>2.118183500686833</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.0961151549238605</v>
+        <v>0.09609749696144332</v>
       </c>
       <c r="C73">
-        <v>135.7193207375032</v>
+        <v>130.2167972845019</v>
       </c>
       <c r="D73">
-        <v>382.4243207375031</v>
+        <v>382.4767972845019</v>
       </c>
       <c r="E73">
-        <v>57.60499999999996</v>
+        <v>63.15999999999997</v>
       </c>
       <c r="F73">
-        <v>394.405</v>
+        <v>399.96</v>
       </c>
       <c r="G73">
         <v>147.7</v>
@@ -7261,28 +7261,28 @@
         <v>63.325</v>
       </c>
       <c r="M73">
-        <v>29.895899</v>
+        <v>30.316968</v>
       </c>
       <c r="N73">
-        <v>33.429101</v>
+        <v>33.008032</v>
       </c>
       <c r="O73">
-        <v>8.3372177894</v>
+        <v>8.232203180800001</v>
       </c>
       <c r="P73">
-        <v>25.0918832106</v>
+        <v>24.7758288192</v>
       </c>
       <c r="Q73">
-        <v>61.3918832106</v>
+        <v>61.0758288192</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1921357383581396</v>
+        <v>0.1969026834337262</v>
       </c>
       <c r="T73">
-        <v>3.379578253074818</v>
+        <v>3.4896693633655</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.118183500686833</v>
+        <v>2.088764285399516</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09609749696144332</v>
+        <v>0.09607983899902614</v>
       </c>
       <c r="C74">
-        <v>130.2167972845019</v>
+        <v>124.714288235218</v>
       </c>
       <c r="D74">
-        <v>382.4767972845019</v>
+        <v>382.529288235218</v>
       </c>
       <c r="E74">
-        <v>63.15999999999997</v>
+        <v>68.71499999999997</v>
       </c>
       <c r="F74">
-        <v>399.96</v>
+        <v>405.515</v>
       </c>
       <c r="G74">
         <v>147.7</v>
@@ -7343,28 +7343,28 @@
         <v>63.325</v>
       </c>
       <c r="M74">
-        <v>30.316968</v>
+        <v>30.738037</v>
       </c>
       <c r="N74">
-        <v>33.008032</v>
+        <v>32.586963</v>
       </c>
       <c r="O74">
-        <v>8.232203180800001</v>
+        <v>8.1271885722</v>
       </c>
       <c r="P74">
-        <v>24.7758288192</v>
+        <v>24.4597744278</v>
       </c>
       <c r="Q74">
-        <v>61.0758288192</v>
+        <v>60.7597744278</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1969026834337262</v>
+        <v>0.2020227355519487</v>
       </c>
       <c r="T74">
-        <v>3.4896693633655</v>
+        <v>3.607915370714751</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.088764285399516</v>
+        <v>2.060151076010482</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09607983899902614</v>
+        <v>0.09606218103660899</v>
       </c>
       <c r="C75">
-        <v>124.714288235218</v>
+        <v>119.2117935955824</v>
       </c>
       <c r="D75">
-        <v>382.529288235218</v>
+        <v>382.5817935955824</v>
       </c>
       <c r="E75">
-        <v>68.71499999999997</v>
+        <v>74.26999999999998</v>
       </c>
       <c r="F75">
-        <v>405.515</v>
+        <v>411.07</v>
       </c>
       <c r="G75">
         <v>147.7</v>
@@ -7425,28 +7425,28 @@
         <v>63.325</v>
       </c>
       <c r="M75">
-        <v>30.738037</v>
+        <v>31.159106</v>
       </c>
       <c r="N75">
-        <v>32.586963</v>
+        <v>32.165894</v>
       </c>
       <c r="O75">
-        <v>8.1271885722</v>
+        <v>8.0221739636</v>
       </c>
       <c r="P75">
-        <v>24.4597744278</v>
+        <v>24.1437200364</v>
       </c>
       <c r="Q75">
-        <v>60.7597744278</v>
+        <v>60.44372003639999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2020227355519487</v>
+        <v>0.2075366378331115</v>
       </c>
       <c r="T75">
-        <v>3.607915370714751</v>
+        <v>3.735257224783175</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.060151076010482</v>
+        <v>2.032311196604935</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09606218103660899</v>
+        <v>0.09604452307419181</v>
       </c>
       <c r="C76">
-        <v>119.2117935955824</v>
+        <v>113.7093133715297</v>
       </c>
       <c r="D76">
-        <v>382.5817935955824</v>
+        <v>382.6343133715297</v>
       </c>
       <c r="E76">
-        <v>74.26999999999998</v>
+        <v>79.82499999999999</v>
       </c>
       <c r="F76">
-        <v>411.07</v>
+        <v>416.625</v>
       </c>
       <c r="G76">
         <v>147.7</v>
@@ -7507,28 +7507,28 @@
         <v>63.325</v>
       </c>
       <c r="M76">
-        <v>31.159106</v>
+        <v>31.580175</v>
       </c>
       <c r="N76">
-        <v>32.165894</v>
+        <v>31.744825</v>
       </c>
       <c r="O76">
-        <v>8.0221739636</v>
+        <v>7.917159355</v>
       </c>
       <c r="P76">
-        <v>24.1437200364</v>
+        <v>23.827665645</v>
       </c>
       <c r="Q76">
-        <v>60.44372003639999</v>
+        <v>60.12766564499999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2075366378331115</v>
+        <v>0.2134916522967673</v>
       </c>
       <c r="T76">
-        <v>3.735257224783175</v>
+        <v>3.872786427177074</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.032311196604935</v>
+        <v>2.005213713983535</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09604452307419181</v>
+        <v>0.1041273403117746</v>
       </c>
       <c r="C77">
-        <v>113.7093133715297</v>
+        <v>85.53196571250567</v>
       </c>
       <c r="D77">
-        <v>382.6343133715297</v>
+        <v>360.0119657125057</v>
       </c>
       <c r="E77">
-        <v>79.82499999999999</v>
+        <v>85.38</v>
       </c>
       <c r="F77">
-        <v>416.625</v>
+        <v>422.18</v>
       </c>
       <c r="G77">
         <v>147.7</v>
@@ -7589,45 +7589,45 @@
         <v>63.325</v>
       </c>
       <c r="M77">
-        <v>31.580175</v>
+        <v>37.9962</v>
       </c>
       <c r="N77">
-        <v>31.744825</v>
+        <v>25.3288</v>
       </c>
       <c r="O77">
-        <v>7.917159355</v>
+        <v>6.317002720000001</v>
       </c>
       <c r="P77">
-        <v>23.827665645</v>
+        <v>19.01179728</v>
       </c>
       <c r="Q77">
-        <v>60.12766564499999</v>
+        <v>55.31179727999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2134916522967673</v>
+        <v>0.2199429179657278</v>
       </c>
       <c r="T77">
-        <v>3.872786427177074</v>
+        <v>4.021776396437131</v>
       </c>
       <c r="U77">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V77">
         <v>0.2494</v>
       </c>
       <c r="W77">
-        <v>0.05689548</v>
+        <v>0.06755399999999999</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y77">
-        <v>2.005213713983535</v>
+        <v>1.666614029824035</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1041273403117746</v>
+        <v>0.1042162675493575</v>
       </c>
       <c r="C78">
-        <v>85.53196571250567</v>
+        <v>79.74294174684894</v>
       </c>
       <c r="D78">
-        <v>360.0119657125057</v>
+        <v>359.777941746849</v>
       </c>
       <c r="E78">
-        <v>85.38</v>
+        <v>90.935</v>
       </c>
       <c r="F78">
-        <v>422.18</v>
+        <v>427.735</v>
       </c>
       <c r="G78">
         <v>147.7</v>
@@ -7671,28 +7671,28 @@
         <v>63.325</v>
       </c>
       <c r="M78">
-        <v>37.9962</v>
+        <v>38.49615</v>
       </c>
       <c r="N78">
-        <v>25.3288</v>
+        <v>24.82885</v>
       </c>
       <c r="O78">
-        <v>6.317002720000001</v>
+        <v>6.192315190000001</v>
       </c>
       <c r="P78">
-        <v>19.01179728</v>
+        <v>18.63653481</v>
       </c>
       <c r="Q78">
-        <v>55.31179727999999</v>
+        <v>54.93653481</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2199429179657278</v>
+        <v>0.226955163258076</v>
       </c>
       <c r="T78">
-        <v>4.021776396437131</v>
+        <v>4.183722015198062</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.666614029824035</v>
+        <v>1.644969691774372</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1042162675493575</v>
+        <v>0.1043051947869403</v>
       </c>
       <c r="C79">
-        <v>79.74294174684894</v>
+        <v>73.95422183574436</v>
       </c>
       <c r="D79">
-        <v>359.777941746849</v>
+        <v>359.5442218357444</v>
       </c>
       <c r="E79">
-        <v>90.935</v>
+        <v>96.49000000000001</v>
       </c>
       <c r="F79">
-        <v>427.735</v>
+        <v>433.29</v>
       </c>
       <c r="G79">
         <v>147.7</v>
@@ -7753,28 +7753,28 @@
         <v>63.325</v>
       </c>
       <c r="M79">
-        <v>38.49615</v>
+        <v>38.9961</v>
       </c>
       <c r="N79">
-        <v>24.82885</v>
+        <v>24.3289</v>
       </c>
       <c r="O79">
-        <v>6.192315190000001</v>
+        <v>6.067627660000001</v>
       </c>
       <c r="P79">
-        <v>18.63653481</v>
+        <v>18.26127234</v>
       </c>
       <c r="Q79">
-        <v>54.93653481</v>
+        <v>54.56127234</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.226955163258076</v>
+        <v>0.2346048853951833</v>
       </c>
       <c r="T79">
-        <v>4.183722015198062</v>
+        <v>4.360389962937259</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.644969691774372</v>
+        <v>1.623880336751624</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1043051947869403</v>
+        <v>0.1043941220245232</v>
       </c>
       <c r="C80">
-        <v>73.95422183574436</v>
+        <v>68.16580538701413</v>
       </c>
       <c r="D80">
-        <v>359.5442218357444</v>
+        <v>359.3108053870142</v>
       </c>
       <c r="E80">
-        <v>96.49000000000001</v>
+        <v>102.045</v>
       </c>
       <c r="F80">
-        <v>433.29</v>
+        <v>438.845</v>
       </c>
       <c r="G80">
         <v>147.7</v>
@@ -7835,28 +7835,28 @@
         <v>63.325</v>
       </c>
       <c r="M80">
-        <v>38.9961</v>
+        <v>39.49605</v>
       </c>
       <c r="N80">
-        <v>24.3289</v>
+        <v>23.82895</v>
       </c>
       <c r="O80">
-        <v>6.067627660000001</v>
+        <v>5.94294013</v>
       </c>
       <c r="P80">
-        <v>18.26127234</v>
+        <v>17.88600987</v>
       </c>
       <c r="Q80">
-        <v>54.56127234</v>
+        <v>54.18600986999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2346048853951833</v>
+        <v>0.2429831524977294</v>
       </c>
       <c r="T80">
-        <v>4.360389962937259</v>
+        <v>4.553883429508763</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.623880336751624</v>
+        <v>1.60332488945097</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1043941220245232</v>
+        <v>0.104483049262106</v>
       </c>
       <c r="C81">
-        <v>68.16580538701413</v>
+        <v>62.37769181001772</v>
       </c>
       <c r="D81">
-        <v>359.3108053870142</v>
+        <v>359.0776918100178</v>
       </c>
       <c r="E81">
-        <v>102.045</v>
+        <v>107.6</v>
       </c>
       <c r="F81">
-        <v>438.845</v>
+        <v>444.4</v>
       </c>
       <c r="G81">
         <v>147.7</v>
@@ -7917,28 +7917,28 @@
         <v>63.325</v>
       </c>
       <c r="M81">
-        <v>39.49605</v>
+        <v>39.996</v>
       </c>
       <c r="N81">
-        <v>23.82895</v>
+        <v>23.329</v>
       </c>
       <c r="O81">
-        <v>5.94294013</v>
+        <v>5.8182526</v>
       </c>
       <c r="P81">
-        <v>17.88600987</v>
+        <v>17.5107474</v>
       </c>
       <c r="Q81">
-        <v>54.18600986999999</v>
+        <v>53.8107474</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2429831524977294</v>
+        <v>0.25219924631053</v>
       </c>
       <c r="T81">
-        <v>4.553883429508763</v>
+        <v>4.766726242737414</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.60332488945097</v>
+        <v>1.583283328332833</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.104483049262106</v>
+        <v>0.1045719764996888</v>
       </c>
       <c r="C82">
-        <v>62.37769181001772</v>
+        <v>56.58988051564609</v>
       </c>
       <c r="D82">
-        <v>359.0776918100178</v>
+        <v>358.8448805156461</v>
       </c>
       <c r="E82">
-        <v>107.6</v>
+        <v>113.155</v>
       </c>
       <c r="F82">
-        <v>444.4</v>
+        <v>449.955</v>
       </c>
       <c r="G82">
         <v>147.7</v>
@@ -7999,28 +7999,28 @@
         <v>63.325</v>
       </c>
       <c r="M82">
-        <v>39.996</v>
+        <v>40.49595</v>
       </c>
       <c r="N82">
-        <v>23.329</v>
+        <v>22.82905</v>
       </c>
       <c r="O82">
-        <v>5.8182526</v>
+        <v>5.693565070000001</v>
       </c>
       <c r="P82">
-        <v>17.5107474</v>
+        <v>17.13548493</v>
       </c>
       <c r="Q82">
-        <v>53.8107474</v>
+        <v>53.43548493</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.25219924631053</v>
+        <v>0.2623854552615202</v>
       </c>
       <c r="T82">
-        <v>4.766726242737414</v>
+        <v>5.001973562621714</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.583283328332833</v>
+        <v>1.563736620575638</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1045719764996888</v>
+        <v>0.1046609037372717</v>
       </c>
       <c r="C83">
-        <v>56.58988051564609</v>
+        <v>50.80237091631716</v>
       </c>
       <c r="D83">
-        <v>358.8448805156461</v>
+        <v>358.6123709163172</v>
       </c>
       <c r="E83">
-        <v>113.155</v>
+        <v>118.71</v>
       </c>
       <c r="F83">
-        <v>449.955</v>
+        <v>455.51</v>
       </c>
       <c r="G83">
         <v>147.7</v>
@@ -8081,28 +8081,28 @@
         <v>63.325</v>
       </c>
       <c r="M83">
-        <v>40.49595</v>
+        <v>40.99590000000001</v>
       </c>
       <c r="N83">
-        <v>22.82905</v>
+        <v>22.3291</v>
       </c>
       <c r="O83">
-        <v>5.693565070000001</v>
+        <v>5.568877539999999</v>
       </c>
       <c r="P83">
-        <v>17.13548493</v>
+        <v>16.76022246</v>
       </c>
       <c r="Q83">
-        <v>53.43548493</v>
+        <v>53.06022245999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2623854552615202</v>
+        <v>0.2737034652070649</v>
       </c>
       <c r="T83">
-        <v>5.001973562621714</v>
+        <v>5.263359473604271</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.563736620575638</v>
+        <v>1.54466666178813</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1046609037372717</v>
+        <v>0.1047498309748545</v>
       </c>
       <c r="C84">
-        <v>50.80237091631716</v>
+        <v>45.01516242597074</v>
       </c>
       <c r="D84">
-        <v>358.6123709163172</v>
+        <v>358.3801624259708</v>
       </c>
       <c r="E84">
-        <v>118.71</v>
+        <v>124.265</v>
       </c>
       <c r="F84">
-        <v>455.51</v>
+        <v>461.0650000000001</v>
       </c>
       <c r="G84">
         <v>147.7</v>
@@ -8163,28 +8163,28 @@
         <v>63.325</v>
       </c>
       <c r="M84">
-        <v>40.99590000000001</v>
+        <v>41.49585</v>
       </c>
       <c r="N84">
-        <v>22.3291</v>
+        <v>21.82915</v>
       </c>
       <c r="O84">
-        <v>5.568877539999999</v>
+        <v>5.44419001</v>
       </c>
       <c r="P84">
-        <v>16.76022246</v>
+        <v>16.38495999</v>
       </c>
       <c r="Q84">
-        <v>53.06022245999999</v>
+        <v>52.68495999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2737034652070649</v>
+        <v>0.2863530057344383</v>
       </c>
       <c r="T84">
-        <v>5.263359473604271</v>
+        <v>5.555496668231832</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.54466666178813</v>
+        <v>1.526056220079839</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1047498309748545</v>
+        <v>0.1048387582124373</v>
       </c>
       <c r="C85">
-        <v>45.01516242597074</v>
+        <v>39.22825446006345</v>
       </c>
       <c r="D85">
-        <v>358.3801624259708</v>
+        <v>358.1482544600635</v>
       </c>
       <c r="E85">
-        <v>124.265</v>
+        <v>129.8200000000001</v>
       </c>
       <c r="F85">
-        <v>461.0650000000001</v>
+        <v>466.6200000000001</v>
       </c>
       <c r="G85">
         <v>147.7</v>
@@ -8245,28 +8245,28 @@
         <v>63.325</v>
       </c>
       <c r="M85">
-        <v>41.49585</v>
+        <v>41.9958</v>
       </c>
       <c r="N85">
-        <v>21.82915</v>
+        <v>21.3292</v>
       </c>
       <c r="O85">
-        <v>5.44419001</v>
+        <v>5.319502480000001</v>
       </c>
       <c r="P85">
-        <v>16.38495999</v>
+        <v>16.00969752</v>
       </c>
       <c r="Q85">
-        <v>52.68495999</v>
+        <v>52.30969752</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2863530057344383</v>
+        <v>0.3005837388277335</v>
       </c>
       <c r="T85">
-        <v>5.555496668231832</v>
+        <v>5.884151012187841</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.526056220079839</v>
+        <v>1.507888884126508</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1048387582124373</v>
+        <v>0.1448008440277062</v>
       </c>
       <c r="C86">
-        <v>39.22825446006351</v>
+        <v>-47.01141791423851</v>
       </c>
       <c r="D86">
-        <v>358.1482544600635</v>
+        <v>277.4635820857615</v>
       </c>
       <c r="E86">
-        <v>129.82</v>
+        <v>135.375</v>
       </c>
       <c r="F86">
-        <v>466.62</v>
+        <v>472.175</v>
       </c>
       <c r="G86">
         <v>147.7</v>
@@ -8327,45 +8327,45 @@
         <v>63.325</v>
       </c>
       <c r="M86">
-        <v>41.9958</v>
+        <v>69.31529</v>
       </c>
       <c r="N86">
-        <v>21.32920000000001</v>
+        <v>-5.990290000000002</v>
       </c>
       <c r="O86">
-        <v>5.319502480000002</v>
+        <v>-1.493978326000001</v>
       </c>
       <c r="P86">
-        <v>16.00969752</v>
+        <v>-4.496311674000001</v>
       </c>
       <c r="Q86">
-        <v>52.30969752</v>
+        <v>31.803688326</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3005837388277333</v>
+        <v>0.3230103073194214</v>
       </c>
       <c r="T86">
-        <v>5.884151012187838</v>
+        <v>6.402085619386176</v>
       </c>
       <c r="U86">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2494</v>
+        <v>0.2278466266245153</v>
       </c>
       <c r="W86">
-        <v>0.06755399999999999</v>
+        <v>0.1133521152115212</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y86">
-        <v>1.507888884126508</v>
+        <v>0.9135790963292514</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1448008440277062</v>
+        <v>0.1458108440277062</v>
       </c>
       <c r="C87">
-        <v>-47.01141791423851</v>
+        <v>-54.13729298319754</v>
       </c>
       <c r="D87">
-        <v>277.4635820857615</v>
+        <v>275.8927070168025</v>
       </c>
       <c r="E87">
-        <v>135.375</v>
+        <v>140.93</v>
       </c>
       <c r="F87">
-        <v>472.175</v>
+        <v>477.73</v>
       </c>
       <c r="G87">
         <v>147.7</v>
@@ -8409,37 +8409,37 @@
         <v>63.325</v>
       </c>
       <c r="M87">
-        <v>69.31529</v>
+        <v>70.13076400000001</v>
       </c>
       <c r="N87">
-        <v>-5.990290000000002</v>
+        <v>-6.805764000000011</v>
       </c>
       <c r="O87">
-        <v>-1.493978326000001</v>
+        <v>-1.697357541600003</v>
       </c>
       <c r="P87">
-        <v>-4.496311674000001</v>
+        <v>-5.108406458400008</v>
       </c>
       <c r="Q87">
-        <v>31.803688326</v>
+        <v>31.19159354159999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3230103073194214</v>
+        <v>0.3428110435565228</v>
       </c>
       <c r="T87">
-        <v>6.402085619386176</v>
+        <v>6.85937744934233</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2278466266245153</v>
+        <v>0.2251972472451605</v>
       </c>
       <c r="W87">
-        <v>0.1133521152115212</v>
+        <v>0.1137410441044105</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.9135790963292514</v>
+        <v>0.9029560835812368</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1458108440277062</v>
+        <v>0.1468208440277062</v>
       </c>
       <c r="C88">
-        <v>-54.13729298319754</v>
+        <v>-61.24548100011691</v>
       </c>
       <c r="D88">
-        <v>275.8927070168025</v>
+        <v>274.3395189998831</v>
       </c>
       <c r="E88">
-        <v>140.93</v>
+        <v>146.485</v>
       </c>
       <c r="F88">
-        <v>477.73</v>
+        <v>483.285</v>
       </c>
       <c r="G88">
         <v>147.7</v>
@@ -8491,37 +8491,37 @@
         <v>63.325</v>
       </c>
       <c r="M88">
-        <v>70.13076400000001</v>
+        <v>70.94623800000001</v>
       </c>
       <c r="N88">
-        <v>-6.805764000000011</v>
+        <v>-7.621238000000005</v>
       </c>
       <c r="O88">
-        <v>-1.697357541600003</v>
+        <v>-1.900736757200001</v>
       </c>
       <c r="P88">
-        <v>-5.108406458400008</v>
+        <v>-5.720501242800004</v>
       </c>
       <c r="Q88">
-        <v>31.19159354159999</v>
+        <v>30.57949875719999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3428110435565228</v>
+        <v>0.3656580469070246</v>
       </c>
       <c r="T88">
-        <v>6.85937744934233</v>
+        <v>7.38702186852251</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2251972472451605</v>
+        <v>0.2226087731388943</v>
       </c>
       <c r="W88">
-        <v>0.1137410441044105</v>
+        <v>0.1141210321032103</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.9029560835812368</v>
+        <v>0.8925772780228318</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1468208440277062</v>
+        <v>0.1478308440277062</v>
       </c>
       <c r="C89">
-        <v>-61.24548100011691</v>
+        <v>-68.33627901012619</v>
       </c>
       <c r="D89">
-        <v>274.3395189998831</v>
+        <v>272.8037209898738</v>
       </c>
       <c r="E89">
-        <v>146.485</v>
+        <v>152.04</v>
       </c>
       <c r="F89">
-        <v>483.285</v>
+        <v>488.84</v>
       </c>
       <c r="G89">
         <v>147.7</v>
@@ -8573,37 +8573,37 @@
         <v>63.325</v>
       </c>
       <c r="M89">
-        <v>70.94623800000001</v>
+        <v>71.761712</v>
       </c>
       <c r="N89">
-        <v>-7.621238000000005</v>
+        <v>-8.436712</v>
       </c>
       <c r="O89">
-        <v>-1.900736757200001</v>
+        <v>-2.1041159728</v>
       </c>
       <c r="P89">
-        <v>-5.720501242800004</v>
+        <v>-6.332596027199999</v>
       </c>
       <c r="Q89">
-        <v>30.57949875719999</v>
+        <v>29.9674039728</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3656580469070246</v>
+        <v>0.3923128841492767</v>
       </c>
       <c r="T89">
-        <v>7.38702186852251</v>
+        <v>8.00260702423272</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2226087731388943</v>
+        <v>0.2200791279895886</v>
       </c>
       <c r="W89">
-        <v>0.1141210321032103</v>
+        <v>0.1144923840111284</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8925772780228318</v>
+        <v>0.882434354408936</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1478308440277062</v>
+        <v>0.1488408440277062</v>
       </c>
       <c r="C90">
-        <v>-68.33627901012619</v>
+        <v>-75.40997744375363</v>
       </c>
       <c r="D90">
-        <v>272.8037209898738</v>
+        <v>271.2850225562464</v>
       </c>
       <c r="E90">
-        <v>152.04</v>
+        <v>157.595</v>
       </c>
       <c r="F90">
-        <v>488.84</v>
+        <v>494.395</v>
       </c>
       <c r="G90">
         <v>147.7</v>
@@ -8655,37 +8655,37 @@
         <v>63.325</v>
       </c>
       <c r="M90">
-        <v>71.761712</v>
+        <v>72.577186</v>
       </c>
       <c r="N90">
-        <v>-8.436712</v>
+        <v>-9.252185999999995</v>
       </c>
       <c r="O90">
-        <v>-2.1041159728</v>
+        <v>-2.307495188399999</v>
       </c>
       <c r="P90">
-        <v>-6.332596027199999</v>
+        <v>-6.944690811599996</v>
       </c>
       <c r="Q90">
-        <v>29.9674039728</v>
+        <v>29.3553091884</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3923128841492767</v>
+        <v>0.4238140554355745</v>
       </c>
       <c r="T90">
-        <v>8.00260702423272</v>
+        <v>8.730116753708421</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.2200791279895886</v>
+        <v>0.2176063287986944</v>
       </c>
       <c r="W90">
-        <v>0.1144923840111284</v>
+        <v>0.1148553909323517</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.882434354408936</v>
+        <v>0.8725193616627683</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1488408440277062</v>
+        <v>0.1498508440277062</v>
       </c>
       <c r="C91">
-        <v>-75.40997744375363</v>
+        <v>-82.466860300024</v>
       </c>
       <c r="D91">
-        <v>271.2850225562464</v>
+        <v>269.783139699976</v>
       </c>
       <c r="E91">
-        <v>157.595</v>
+        <v>163.15</v>
       </c>
       <c r="F91">
-        <v>494.395</v>
+        <v>499.95</v>
       </c>
       <c r="G91">
         <v>147.7</v>
@@ -8737,37 +8737,37 @@
         <v>63.325</v>
       </c>
       <c r="M91">
-        <v>72.577186</v>
+        <v>73.39266000000001</v>
       </c>
       <c r="N91">
-        <v>-9.252185999999995</v>
+        <v>-10.06766</v>
       </c>
       <c r="O91">
-        <v>-2.307495188399999</v>
+        <v>-2.510874404000001</v>
       </c>
       <c r="P91">
-        <v>-6.944690811599996</v>
+        <v>-7.556785596000003</v>
       </c>
       <c r="Q91">
-        <v>29.3553091884</v>
+        <v>28.74321440399999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4238140554355745</v>
+        <v>0.4616154609791321</v>
       </c>
       <c r="T91">
-        <v>8.730116753708421</v>
+        <v>9.603128429079264</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.2176063287986944</v>
+        <v>0.2151884807009311</v>
       </c>
       <c r="W91">
-        <v>0.1148553909323517</v>
+        <v>0.1152103310331033</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8725193616627683</v>
+        <v>0.8628247020887374</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1498508440277062</v>
+        <v>0.1508608440277062</v>
       </c>
       <c r="C92">
-        <v>-82.466860300024</v>
+        <v>-89.50720532350834</v>
       </c>
       <c r="D92">
-        <v>269.783139699976</v>
+        <v>268.2977946764917</v>
       </c>
       <c r="E92">
-        <v>163.15</v>
+        <v>168.705</v>
       </c>
       <c r="F92">
-        <v>499.95</v>
+        <v>505.505</v>
       </c>
       <c r="G92">
         <v>147.7</v>
@@ -8819,37 +8819,37 @@
         <v>63.325</v>
       </c>
       <c r="M92">
-        <v>73.39266000000001</v>
+        <v>74.208134</v>
       </c>
       <c r="N92">
-        <v>-10.06766</v>
+        <v>-10.883134</v>
       </c>
       <c r="O92">
-        <v>-2.510874404000001</v>
+        <v>-2.7142536196</v>
       </c>
       <c r="P92">
-        <v>-7.556785596000003</v>
+        <v>-8.168880380399999</v>
       </c>
       <c r="Q92">
-        <v>28.74321440399999</v>
+        <v>28.1311196196</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4616154609791321</v>
+        <v>0.5078171788657023</v>
       </c>
       <c r="T92">
-        <v>9.603128429079264</v>
+        <v>10.67014269897696</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2151884807009311</v>
+        <v>0.2128237721218</v>
       </c>
       <c r="W92">
-        <v>0.1152103310331033</v>
+        <v>0.1155574702525198</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8628247020887374</v>
+        <v>0.8533431119558943</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1508608440277062</v>
+        <v>0.1518708440277062</v>
       </c>
       <c r="C93">
-        <v>-89.50720532350834</v>
+        <v>-96.53128417555712</v>
       </c>
       <c r="D93">
-        <v>268.2977946764917</v>
+        <v>266.8287158244429</v>
       </c>
       <c r="E93">
-        <v>168.705</v>
+        <v>174.26</v>
       </c>
       <c r="F93">
-        <v>505.505</v>
+        <v>511.06</v>
       </c>
       <c r="G93">
         <v>147.7</v>
@@ -8901,37 +8901,37 @@
         <v>63.325</v>
       </c>
       <c r="M93">
-        <v>74.208134</v>
+        <v>75.02360800000001</v>
       </c>
       <c r="N93">
-        <v>-10.883134</v>
+        <v>-11.69860800000001</v>
       </c>
       <c r="O93">
-        <v>-2.7142536196</v>
+        <v>-2.917632835200002</v>
       </c>
       <c r="P93">
-        <v>-8.168880380399999</v>
+        <v>-8.780975164800005</v>
       </c>
       <c r="Q93">
-        <v>28.1311196196</v>
+        <v>27.51902483519999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5078171788657023</v>
+        <v>0.5655693262239153</v>
       </c>
       <c r="T93">
-        <v>10.67014269897696</v>
+        <v>12.00391053634909</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2128237721218</v>
+        <v>0.2105104702509109</v>
       </c>
       <c r="W93">
-        <v>0.1155574702525198</v>
+        <v>0.1158970629671663</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8533431119558943</v>
+        <v>0.8440676433476779</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1518708440277062</v>
+        <v>0.1528808440277062</v>
       </c>
       <c r="C94">
-        <v>-96.53128417555712</v>
+        <v>-103.539362599938</v>
       </c>
       <c r="D94">
-        <v>266.8287158244429</v>
+        <v>265.375637400062</v>
       </c>
       <c r="E94">
-        <v>174.26</v>
+        <v>179.815</v>
       </c>
       <c r="F94">
-        <v>511.06</v>
+        <v>516.615</v>
       </c>
       <c r="G94">
         <v>147.7</v>
@@ -8983,37 +8983,37 @@
         <v>63.325</v>
       </c>
       <c r="M94">
-        <v>75.02360800000001</v>
+        <v>75.839082</v>
       </c>
       <c r="N94">
-        <v>-11.69860800000001</v>
+        <v>-12.514082</v>
       </c>
       <c r="O94">
-        <v>-2.917632835200002</v>
+        <v>-3.121012050800001</v>
       </c>
       <c r="P94">
-        <v>-8.780975164800005</v>
+        <v>-9.393069949200001</v>
       </c>
       <c r="Q94">
-        <v>27.51902483519999</v>
+        <v>26.9069300508</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5655693262239153</v>
+        <v>0.639822087113046</v>
       </c>
       <c r="T94">
-        <v>12.00391053634909</v>
+        <v>13.71875489868467</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2105104702509109</v>
+        <v>0.2082469168073527</v>
       </c>
       <c r="W94">
-        <v>0.1158970629671663</v>
+        <v>0.1162293526126806</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8440676433476779</v>
+        <v>0.8349916471826492</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1528808440277062</v>
+        <v>0.1538908440277062</v>
       </c>
       <c r="C95">
-        <v>-103.539362599938</v>
+        <v>-110.5317005830914</v>
       </c>
       <c r="D95">
-        <v>265.375637400062</v>
+        <v>263.9382994169086</v>
       </c>
       <c r="E95">
-        <v>179.815</v>
+        <v>185.3700000000001</v>
       </c>
       <c r="F95">
-        <v>516.615</v>
+        <v>522.1700000000001</v>
       </c>
       <c r="G95">
         <v>147.7</v>
@@ -9065,37 +9065,37 @@
         <v>63.325</v>
       </c>
       <c r="M95">
-        <v>75.839082</v>
+        <v>76.65455600000001</v>
       </c>
       <c r="N95">
-        <v>-12.514082</v>
+        <v>-13.32955600000001</v>
       </c>
       <c r="O95">
-        <v>-3.121012050800001</v>
+        <v>-3.324391266400003</v>
       </c>
       <c r="P95">
-        <v>-9.393069949200001</v>
+        <v>-10.00516473360001</v>
       </c>
       <c r="Q95">
-        <v>26.9069300508</v>
+        <v>26.29483526639999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.639822087113046</v>
+        <v>0.738825768298554</v>
       </c>
       <c r="T95">
-        <v>13.71875489868467</v>
+        <v>16.00521404846545</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2082469168073527</v>
+        <v>0.2060315240753596</v>
       </c>
       <c r="W95">
-        <v>0.1162293526126806</v>
+        <v>0.1165545722657372</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8349916471826492</v>
+        <v>0.8261087573190038</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1538908440277062</v>
+        <v>0.1549008440277062</v>
       </c>
       <c r="C96">
-        <v>-110.5317005830914</v>
+        <v>-117.5085525092054</v>
       </c>
       <c r="D96">
-        <v>263.9382994169086</v>
+        <v>262.5164474907946</v>
       </c>
       <c r="E96">
-        <v>185.3700000000001</v>
+        <v>190.925</v>
       </c>
       <c r="F96">
-        <v>522.1700000000001</v>
+        <v>527.725</v>
       </c>
       <c r="G96">
         <v>147.7</v>
@@ -9147,37 +9147,37 @@
         <v>63.325</v>
       </c>
       <c r="M96">
-        <v>76.65455600000001</v>
+        <v>77.47003000000001</v>
       </c>
       <c r="N96">
-        <v>-13.32955600000001</v>
+        <v>-14.14503000000001</v>
       </c>
       <c r="O96">
-        <v>-3.324391266400003</v>
+        <v>-3.527770482000002</v>
       </c>
       <c r="P96">
-        <v>-10.00516473360001</v>
+        <v>-10.617259518</v>
       </c>
       <c r="Q96">
-        <v>26.29483526639999</v>
+        <v>25.68274048199999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.738825768298554</v>
+        <v>0.8774309219582651</v>
       </c>
       <c r="T96">
-        <v>16.00521404846545</v>
+        <v>19.20625685815855</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2060315240753596</v>
+        <v>0.2038627711903558</v>
       </c>
       <c r="W96">
-        <v>0.1165545722657372</v>
+        <v>0.1168729451892558</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8261087573190038</v>
+        <v>0.8174128756630143</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1549008440277062</v>
+        <v>0.1559108440277062</v>
       </c>
       <c r="C97">
-        <v>-117.5085525092054</v>
+        <v>-124.4701673103061</v>
       </c>
       <c r="D97">
-        <v>262.5164474907946</v>
+        <v>261.109832689694</v>
       </c>
       <c r="E97">
-        <v>190.925</v>
+        <v>196.4800000000001</v>
       </c>
       <c r="F97">
-        <v>527.725</v>
+        <v>533.2800000000001</v>
       </c>
       <c r="G97">
         <v>147.7</v>
@@ -9229,37 +9229,37 @@
         <v>63.325</v>
       </c>
       <c r="M97">
-        <v>77.47003000000001</v>
+        <v>78.28550400000002</v>
       </c>
       <c r="N97">
-        <v>-14.14503000000001</v>
+        <v>-14.96050400000001</v>
       </c>
       <c r="O97">
-        <v>-3.527770482000002</v>
+        <v>-3.731149697600004</v>
       </c>
       <c r="P97">
-        <v>-10.617259518</v>
+        <v>-11.22935430240001</v>
       </c>
       <c r="Q97">
-        <v>25.68274048199999</v>
+        <v>25.07064569759999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8774309219582651</v>
+        <v>1.085338652447832</v>
       </c>
       <c r="T97">
-        <v>19.20625685815855</v>
+        <v>24.0078210726982</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.2038627711903558</v>
+        <v>0.2017392006571229</v>
       </c>
       <c r="W97">
-        <v>0.1168729451892558</v>
+        <v>0.1171846853435344</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8174128756630143</v>
+        <v>0.8088981582081912</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1559108440277062</v>
+        <v>0.1569208440277062</v>
       </c>
       <c r="C98">
-        <v>-124.4701673103059</v>
+        <v>-131.4167886115472</v>
       </c>
       <c r="D98">
-        <v>261.1098326896941</v>
+        <v>259.7182113884528</v>
       </c>
       <c r="E98">
-        <v>196.48</v>
+        <v>202.035</v>
       </c>
       <c r="F98">
-        <v>533.28</v>
+        <v>538.835</v>
       </c>
       <c r="G98">
         <v>147.7</v>
@@ -9311,37 +9311,37 @@
         <v>63.325</v>
       </c>
       <c r="M98">
-        <v>78.285504</v>
+        <v>79.10097800000001</v>
       </c>
       <c r="N98">
-        <v>-14.960504</v>
+        <v>-15.77597800000001</v>
       </c>
       <c r="O98">
-        <v>-3.7311496976</v>
+        <v>-3.934528913200003</v>
       </c>
       <c r="P98">
-        <v>-11.2293543024</v>
+        <v>-11.84144908680001</v>
       </c>
       <c r="Q98">
-        <v>25.0706456976</v>
+        <v>24.45855091319999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.085338652447829</v>
+        <v>1.431851536597106</v>
       </c>
       <c r="T98">
-        <v>24.00782107269814</v>
+        <v>32.01042809693085</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.2017392006571229</v>
+        <v>0.1996594150833381</v>
       </c>
       <c r="W98">
-        <v>0.1171846853435344</v>
+        <v>0.117489997865766</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8088981582081913</v>
+        <v>0.8005590019380038</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1569208440277062</v>
+        <v>0.2135366782135058</v>
       </c>
       <c r="C99">
-        <v>-131.4167886115472</v>
+        <v>-196.715160999677</v>
       </c>
       <c r="D99">
-        <v>259.7182113884528</v>
+        <v>199.974839000323</v>
       </c>
       <c r="E99">
-        <v>202.035</v>
+        <v>207.59</v>
       </c>
       <c r="F99">
-        <v>538.835</v>
+        <v>544.39</v>
       </c>
       <c r="G99">
         <v>147.7</v>
@@ -9393,45 +9393,45 @@
         <v>63.325</v>
       </c>
       <c r="M99">
-        <v>79.10097800000001</v>
+        <v>109.313512</v>
       </c>
       <c r="N99">
-        <v>-15.77597800000001</v>
+        <v>-45.988512</v>
       </c>
       <c r="O99">
-        <v>-3.934528913200003</v>
+        <v>-11.4695348928</v>
       </c>
       <c r="P99">
-        <v>-11.84144908680001</v>
+        <v>-34.5189771072</v>
       </c>
       <c r="Q99">
-        <v>24.45855091319999</v>
+        <v>1.781022892799996</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.431851536597106</v>
+        <v>2.259169014185639</v>
       </c>
       <c r="T99">
-        <v>32.01042809693085</v>
+        <v>51.11706730220877</v>
       </c>
       <c r="U99">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1996594150833381</v>
+        <v>0.1444766956165492</v>
       </c>
       <c r="W99">
-        <v>0.117489997865766</v>
+        <v>0.1717890795201969</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.8005590019380038</v>
+        <v>0.5792970954953858</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2135366782135058</v>
+        <v>0.2150866782135058</v>
       </c>
       <c r="C100">
-        <v>-196.715160999677</v>
+        <v>-203.5216585366273</v>
       </c>
       <c r="D100">
-        <v>199.974839000323</v>
+        <v>198.7233414633727</v>
       </c>
       <c r="E100">
-        <v>207.59</v>
+        <v>213.145</v>
       </c>
       <c r="F100">
-        <v>544.39</v>
+        <v>549.9450000000001</v>
       </c>
       <c r="G100">
         <v>147.7</v>
@@ -9475,37 +9475,37 @@
         <v>63.325</v>
       </c>
       <c r="M100">
-        <v>109.313512</v>
+        <v>110.428956</v>
       </c>
       <c r="N100">
-        <v>-45.988512</v>
+        <v>-47.10395600000001</v>
       </c>
       <c r="O100">
-        <v>-11.4695348928</v>
+        <v>-11.7477266264</v>
       </c>
       <c r="P100">
-        <v>-34.5189771072</v>
+        <v>-35.35622937360001</v>
       </c>
       <c r="Q100">
-        <v>1.781022892799996</v>
+        <v>0.9437706263999885</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.259169014185639</v>
+        <v>4.472538028371278</v>
       </c>
       <c r="T100">
-        <v>51.11706730220877</v>
+        <v>102.2341346044175</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1444766956165492</v>
+        <v>0.1430173350547659</v>
       </c>
       <c r="W100">
-        <v>0.1717890795201969</v>
+        <v>0.172082119121003</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5792970954953858</v>
+        <v>0.5734456096823011</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2150866782135058</v>
-      </c>
-      <c r="C101">
-        <v>-203.5216585366273</v>
-      </c>
-      <c r="D101">
-        <v>198.7233414633727</v>
-      </c>
-      <c r="E101">
-        <v>213.145</v>
-      </c>
-      <c r="F101">
-        <v>549.9450000000001</v>
-      </c>
-      <c r="G101">
-        <v>147.7</v>
-      </c>
-      <c r="H101">
-        <v>218.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>99.625</v>
-      </c>
-      <c r="K101">
-        <v>36.3</v>
-      </c>
-      <c r="L101">
-        <v>63.325</v>
-      </c>
-      <c r="M101">
-        <v>110.428956</v>
-      </c>
-      <c r="N101">
-        <v>-47.10395600000001</v>
-      </c>
-      <c r="O101">
-        <v>-11.7477266264</v>
-      </c>
-      <c r="P101">
-        <v>-35.35622937360001</v>
-      </c>
-      <c r="Q101">
-        <v>0.9437706263999885</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.472538028371278</v>
-      </c>
-      <c r="T101">
-        <v>102.2341346044175</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1430173350547659</v>
-      </c>
-      <c r="W101">
-        <v>0.172082119121003</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5734456096823011</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
